--- a/READING/3_22_07.xlsx
+++ b/READING/3_22_07.xlsx
@@ -481,37 +481,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>なし</t>
+          <t>取り組む</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>没有，无</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>あり-&gt;有</t>
-        </is>
-      </c>
+          <t>致力于，专心从事</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>とりくむ</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>なくす</t>
+          <t>おそらく</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>弄丢，消除</t>
+          <t>大概，恐怕</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -519,37 +519,33 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>親子</t>
+          <t>みたいに</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>父母与子女，亲子</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>おやこ</t>
-        </is>
-      </c>
+          <t>像...一样</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>コツ</t>
+          <t>〜たとたんに</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>诀窍，窍门</t>
+          <t>刚一...就...</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -557,16 +553,16 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>なければ</t>
+          <t>どんなに〜でも</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>如果不...的话</t>
+          <t>无论多么......也</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -574,23 +570,19 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>無断</t>
+          <t>〜となります</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>擅自，私自</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>むだん</t>
-        </is>
-      </c>
+          <t>规定…</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
@@ -599,71 +591,75 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>見回る</t>
+          <t>繰返する</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>巡视，环视</t>
+          <t>重复</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>みまわる</t>
+          <t>くりかえしする</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>注意する</t>
+          <t>逃げ続ける</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>注意；警告</t>
+          <t>持续逃跑</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>ちゅういする</t>
+          <t>にげつづける</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ように</t>
+          <t>得をする</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>为了...；像...一样</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>获利，占便宜</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>とくをする</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>きちんと</t>
+          <t>やみくもに</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>好好地，整洁地</t>
+          <t>盲目地，胡乱地</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -671,23 +667,19 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>検討</t>
+          <t>かなりある</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>讨论，研究</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>けんとう</t>
-        </is>
-      </c>
+          <t>有很多</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
     </row>
     <row r="14">
@@ -696,19 +688,15 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>詰まる</t>
+          <t>押しつけ</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>堵塞，塞满</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>つまる</t>
-        </is>
-      </c>
+          <t>强加于人</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
     </row>
     <row r="15">
@@ -717,19 +705,15 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>流れ</t>
+          <t>できるだけ</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>流程，流逝</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>ながれ</t>
-        </is>
-      </c>
+          <t>尽可能地，尽量</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
     </row>
     <row r="16">
@@ -738,20 +722,16 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>といえば</t>
+          <t>いったん</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>说起...</t>
+          <t>一旦；暂时</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>たとえば→比如</t>
-        </is>
-      </c>
+      <c r="E16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -759,12 +739,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>セール</t>
+          <t>どっぷり</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>甩卖，大减价</t>
+          <t>完全陷入</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -772,79 +752,75 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>少なくとも</t>
+          <t>やっかいな</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>至少</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>すくなくとも</t>
-        </is>
-      </c>
+          <t>麻烦的，棘手的</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>教える</t>
+          <t>決まり文句</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>教，告诉</t>
+          <t>口头禅，常用语，客套话</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>おしえる</t>
+          <t>きまりもんく</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>抑える</t>
+          <t>まっすぐ</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>胜过;击败</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>おさえる</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr"/>
+          <t>笔直地，直接地</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>ちょくせつ-&gt;直接</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>トップ</t>
+          <t>ようとする</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>顶端，最高处</t>
+          <t>正想要做...，试图做...</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -856,12 +832,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>つまらない</t>
+          <t>それくらい</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>无聊的</t>
+          <t>那种程度</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -869,16 +845,16 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>すなわち</t>
+          <t>さっさと</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>也就是说，换言之</t>
+          <t>赶快地，迅速地</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -886,16 +862,16 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>かなりある</t>
+          <t>すなわち</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>有很多</t>
+          <t>也就是说，换言之</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -907,32 +883,40 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>それくらい</t>
+          <t>といえば</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>那种程度</t>
+          <t>说起...</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>たとえば→比如</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>すごく</t>
+          <t>見回る</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>非常</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
+          <t>巡视，环视</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>みまわる</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr"/>
     </row>
     <row r="27">
@@ -941,29 +925,33 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>おそらく</t>
+          <t>無断</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>大概，恐怕</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
+          <t>擅自，私自</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>むだん</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>しゃべる</t>
+          <t>つまらない</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>说话，聊天</t>
+          <t>无聊的</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -971,19 +959,23 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>みたいに</t>
+          <t>抑える</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>像...一样</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
+          <t>胜过;击败</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>おさえる</t>
+        </is>
+      </c>
       <c r="E29" t="inlineStr"/>
     </row>
     <row r="30">
@@ -992,101 +984,113 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>〜たとたんに</t>
+          <t>親子</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>刚一...就...</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
+          <t>父母与子女，亲子</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>おやこ</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>祝日</t>
+          <t>コツ</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>节日，法定假日</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>しゅくじつ</t>
-        </is>
-      </c>
+          <t>诀窍，窍门</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>さっさと</t>
+          <t>検討</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>赶快地，迅速地</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr"/>
+          <t>讨论，研究</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>けんとう</t>
+        </is>
+      </c>
       <c r="E32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>なければ</t>
+          <t>詰まる</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>ない的假定型</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr"/>
+          <t>堵塞，塞满</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>つまる</t>
+        </is>
+      </c>
       <c r="E33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>このとおり</t>
+          <t>流れ</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>就照这样</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr"/>
+          <t>流程，流逝</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>ながれ</t>
+        </is>
+      </c>
       <c r="E34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>どんなに〜でも</t>
+          <t>セール</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>无论多么......也</t>
+          <t>甩卖，大减价</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
@@ -1094,16 +1098,16 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>〜となります</t>
+          <t>なければ</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>规定…</t>
+          <t>如果不...的话</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
@@ -1115,20 +1119,20 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>ほかの</t>
+          <t>いつの間に</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>别的，其他的</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>ほかり-&gt;其他的；除…之外，还有…</t>
-        </is>
-      </c>
+          <t>不知不觉地</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>いつのまに</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1136,40 +1140,32 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>繰返する</t>
+          <t>まったく</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>重复</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>くりかえしする</t>
-        </is>
-      </c>
+          <t>完全，简直是</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>逃げ続ける</t>
+          <t>ことで</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>持续逃跑</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>にげつづける</t>
-        </is>
-      </c>
+          <t>通过...，因为...</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr"/>
     </row>
     <row r="40">
@@ -1178,40 +1174,32 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>得をする</t>
+          <t>しっかり</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>获利，占便宜</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>とくをする</t>
-        </is>
-      </c>
+          <t>好好地，牢固地</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>取り組む</t>
+          <t>とは</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>致力于，专心从事</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>とりくむ</t>
-        </is>
-      </c>
+          <t>所谓...；竟然...</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr"/>
     </row>
     <row r="42">
@@ -1220,12 +1208,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>すでに</t>
+          <t>ああいう</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>已经</t>
+          <t>那样的</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
@@ -1237,12 +1225,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>やみくもに</t>
+          <t>とにかく</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>盲目地，胡乱地</t>
+          <t>总之，无论如何</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
@@ -1250,16 +1238,16 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>押しつけ</t>
+          <t>それですむ</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>强加于人</t>
+          <t>那样就行了，那样就解决了</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
@@ -1271,12 +1259,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>だと</t>
+          <t>なくす</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>如果…的话,</t>
+          <t>弄丢，消除</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
@@ -1288,29 +1276,33 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>たがる</t>
+          <t>注意する</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>（第三方）想要...</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr"/>
+          <t>注意；警告</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>ちゅういする</t>
+        </is>
+      </c>
       <c r="E46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>ことで</t>
+          <t>きちんと</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>通过...，因为...</t>
+          <t>好好地，整洁地</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
@@ -1318,16 +1310,16 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>できるだけ</t>
+          <t>たがる</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>尽可能地，尽量</t>
+          <t>（第三方）想要...</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
@@ -1335,16 +1327,16 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>いったん</t>
+          <t>だと</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>一旦；暂时</t>
+          <t>如果…的话,</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
@@ -1352,16 +1344,16 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>どっぷり</t>
+          <t>ように</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>完全陷入</t>
+          <t>为了...；像...一样</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
@@ -1369,16 +1361,16 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>やっかいな</t>
+          <t>すでに</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>麻烦的，棘手的</t>
+          <t>已经</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
@@ -1390,16 +1382,20 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>まったく</t>
+          <t>ほかの</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>完全，简直是</t>
+          <t>别的，其他的</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>ほかり-&gt;其他的；除…之外，还有…</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -1407,17 +1403,17 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>いつの間に</t>
+          <t>少なくとも</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>不知不觉地</t>
+          <t>至少</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>いつのまに</t>
+          <t>すくなくとも</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
@@ -1428,12 +1424,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>しっかり</t>
+          <t>このとおり</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>好好地，牢固地</t>
+          <t>就照这样</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
@@ -1445,12 +1441,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>とは</t>
+          <t>なければ</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>所谓...；竟然...</t>
+          <t>ない的假定型</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
@@ -1458,45 +1454,45 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>決まり文句</t>
+          <t>なし</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>口头禅，常用语，客套话</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>きまりもんく</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr"/>
+          <t>没有，无</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>あり-&gt;有</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>まっすぐ</t>
+          <t>祝日</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>笔直地，直接地</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>ちょくせつ-&gt;直接</t>
-        </is>
-      </c>
+          <t>节日，法定假日</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>しゅくじつ</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -1504,15 +1500,19 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ああいう</t>
+          <t>教える</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>那样的</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr"/>
+          <t>教，告诉</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>おしえる</t>
+        </is>
+      </c>
       <c r="E58" t="inlineStr"/>
     </row>
     <row r="59">
@@ -1521,12 +1521,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>とにかく</t>
+          <t>しゃべる</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>总之，无论如何</t>
+          <t>说话，聊天</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
@@ -1538,12 +1538,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>それですむ</t>
+          <t>トップ</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>那样就行了，那样就解决了</t>
+          <t>顶端，最高处</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
@@ -1551,16 +1551,16 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>ようとする</t>
+          <t>すごく</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>正想要做...，试图做...</t>
+          <t>非常</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>

--- a/READING/3_22_07.xlsx
+++ b/READING/3_22_07.xlsx
@@ -464,19 +464,23 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>〜ばよい</t>
+          <t>検討</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>......就好了</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
+          <t>讨论，研究</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>けんとう</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
@@ -485,50 +489,54 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>取り組む</t>
+          <t>流れ</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>致力于，专心从事</t>
+          <t>流程，流逝</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>とりくむ</t>
+          <t>ながれ</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>おそらく</t>
+          <t>抑える</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>大概，恐怕</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>胜过;击败</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>おさえる</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>みたいに</t>
+          <t>すなわち</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>像...一样</t>
+          <t>也就是说，换言之</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -536,16 +544,16 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>〜たとたんに</t>
+          <t>さっさと</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>刚一...就...</t>
+          <t>赶快地，迅速地</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -553,16 +561,16 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>どんなに〜でも</t>
+          <t>コツ</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>无论多么......也</t>
+          <t>诀窍，窍门</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -570,113 +578,117 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>〜となります</t>
+          <t>まっすぐ</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>规定…</t>
+          <t>笔直地，直接地</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>ちょくせつ-&gt;直接</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>繰返する</t>
+          <t>決まり文句</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>重复</t>
+          <t>口头禅，常用语，客套话</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>くりかえしする</t>
+          <t>きまりもんく</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>逃げ続ける</t>
+          <t>やっかいな</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>持续逃跑</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>にげつづける</t>
-        </is>
-      </c>
+          <t>麻烦的，棘手的</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>得をする</t>
+          <t>取り組む</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>获利，占便宜</t>
+          <t>致力于，专心从事</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>とくをする</t>
+          <t>とりくむ</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>やみくもに</t>
+          <t>詰まる</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>盲目地，胡乱地</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>堵塞，塞满</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>つまる</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>かなりある</t>
+          <t>セール</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>有很多</t>
+          <t>甩卖，大减价</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -684,16 +696,16 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>押しつけ</t>
+          <t>かなりある</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>强加于人</t>
+          <t>有很多</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -701,16 +713,16 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>できるだけ</t>
+          <t>やみくもに</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>尽可能地，尽量</t>
+          <t>盲目地，胡乱地</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -718,16 +730,16 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>いったん</t>
+          <t>〜となります</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>一旦；暂时</t>
+          <t>规定…</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -735,16 +747,16 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>どっぷり</t>
+          <t>〜たとたんに</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>完全陷入</t>
+          <t>刚一...就...</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -752,16 +764,16 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>やっかいな</t>
+          <t>みたいに</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>麻烦的，棘手的</t>
+          <t>像...一样</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -769,45 +781,37 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>決まり文句</t>
+          <t>おそらく</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>口头禅，常用语，客套话</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>きまりもんく</t>
-        </is>
-      </c>
+          <t>大概，恐怕</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>まっすぐ</t>
+          <t>つまらない</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>笔直地，直接地</t>
+          <t>无聊的</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>ちょくせつ-&gt;直接</t>
-        </is>
-      </c>
+      <c r="E20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -815,29 +819,33 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ようとする</t>
+          <t>無断</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>正想要做...，试图做...</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
+          <t>擅自，私自</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>むだん</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>それくらい</t>
+          <t>まったく</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>那种程度</t>
+          <t>完全，简直是</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -845,16 +853,16 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>さっさと</t>
+          <t>しっかり</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>赶快地，迅速地</t>
+          <t>好好地，牢固地</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -862,16 +870,16 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>すなわち</t>
+          <t>とにかく</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>也就是说，换言之</t>
+          <t>总之，无论如何</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -883,20 +891,16 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>といえば</t>
+          <t>きちんと</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>说起...</t>
+          <t>好好地，整洁地</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>たとえば→比如</t>
-        </is>
-      </c>
+      <c r="E25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -904,17 +908,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>見回る</t>
+          <t>親子</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>巡视，环视</t>
+          <t>父母与子女，亲子</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>みまわる</t>
+          <t>おやこ</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
@@ -925,19 +929,15 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>無断</t>
+          <t>〜ばよい</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>擅自，私自</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>むだん</t>
-        </is>
-      </c>
+          <t>......就好了</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr"/>
     </row>
     <row r="28">
@@ -946,36 +946,36 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>つまらない</t>
+          <t>見回る</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>无聊的</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
+          <t>巡视，环视</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>みまわる</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>抑える</t>
+          <t>それくらい</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>胜过;击败</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>おさえる</t>
-        </is>
-      </c>
+          <t>那种程度</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr"/>
     </row>
     <row r="30">
@@ -984,19 +984,15 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>親子</t>
+          <t>ようとする</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>父母与子女，亲子</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>おやこ</t>
-        </is>
-      </c>
+          <t>正想要做...，试图做...</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr"/>
     </row>
     <row r="31">
@@ -1005,12 +1001,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>コツ</t>
+          <t>どっぷり</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>诀窍，窍门</t>
+          <t>完全陷入</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -1022,40 +1018,32 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>検討</t>
+          <t>いったん</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>讨论，研究</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>けんとう</t>
-        </is>
-      </c>
+          <t>一旦；暂时</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>詰まる</t>
+          <t>できるだけ</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>堵塞，塞满</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>つまる</t>
-        </is>
-      </c>
+          <t>尽可能地，尽量</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr"/>
     </row>
     <row r="34">
@@ -1064,19 +1052,15 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>流れ</t>
+          <t>押しつけ</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>流程，流逝</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>ながれ</t>
-        </is>
-      </c>
+          <t>强加于人</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
     </row>
     <row r="35">
@@ -1085,29 +1069,33 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>セール</t>
+          <t>得をする</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>甩卖，大减价</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr"/>
+          <t>获利，占便宜</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>とくをする</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>なければ</t>
+          <t>どんなに〜でも</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>如果不...的话</t>
+          <t>无论多么......也</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
@@ -1115,75 +1103,87 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>いつの間に</t>
+          <t>逃げ続ける</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>不知不觉地</t>
+          <t>持续逃跑</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>いつのまに</t>
+          <t>にげつづける</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>まったく</t>
+          <t>といえば</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>完全，简直是</t>
+          <t>说起...</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>たとえば→比如</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>ことで</t>
+          <t>繰返する</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>通过...，因为...</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr"/>
+          <t>重复</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>くりかえしする</t>
+        </is>
+      </c>
       <c r="E39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>しっかり</t>
+          <t>なし</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>好好地，牢固地</t>
+          <t>没有，无</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>あり-&gt;有</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -1191,15 +1191,19 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>とは</t>
+          <t>少なくとも</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>所谓...；竟然...</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr"/>
+          <t>至少</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>すくなくとも</t>
+        </is>
+      </c>
       <c r="E41" t="inlineStr"/>
     </row>
     <row r="42">
@@ -1208,12 +1212,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>ああいう</t>
+          <t>このとおり</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>那样的</t>
+          <t>就照这样</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
@@ -1221,16 +1225,16 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>とにかく</t>
+          <t>なければ</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>总之，无论如何</t>
+          <t>ない的假定型</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
@@ -1242,12 +1246,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>それですむ</t>
+          <t>しゃべる</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>那样就行了，那样就解决了</t>
+          <t>说话，聊天</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
@@ -1259,15 +1263,19 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>なくす</t>
+          <t>祝日</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>弄丢，消除</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr"/>
+          <t>节日，法定假日</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>しゅくじつ</t>
+        </is>
+      </c>
       <c r="E45" t="inlineStr"/>
     </row>
     <row r="46">
@@ -1276,33 +1284,33 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>注意する</t>
+          <t>教える</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>注意；警告</t>
+          <t>教，告诉</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>ちゅういする</t>
+          <t>おしえる</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>きちんと</t>
+          <t>すでに</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>好好地，整洁地</t>
+          <t>已经</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
@@ -1314,12 +1322,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>たがる</t>
+          <t>トップ</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>（第三方）想要...</t>
+          <t>顶端，最高处</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
@@ -1331,12 +1339,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>だと</t>
+          <t>すごく</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>如果…的话,</t>
+          <t>非常</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
@@ -1344,20 +1352,24 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>ように</t>
+          <t>ほかの</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>为了...；像...一样</t>
+          <t>别的，其他的</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>ほかり-&gt;其他的；除…之外，还有…</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -1365,12 +1377,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>すでに</t>
+          <t>なくす</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>已经</t>
+          <t>弄丢，消除</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
@@ -1382,20 +1394,16 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>ほかの</t>
+          <t>ように</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>别的，其他的</t>
+          <t>为了...；像...一样</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>ほかり-&gt;其他的；除…之外，还有…</t>
-        </is>
-      </c>
+      <c r="E52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -1403,19 +1411,15 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>少なくとも</t>
+          <t>だと</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>至少</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>すくなくとも</t>
-        </is>
-      </c>
+          <t>如果…的话,</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr"/>
     </row>
     <row r="54">
@@ -1424,12 +1428,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>このとおり</t>
+          <t>たがる</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>就照这样</t>
+          <t>（第三方）想要...</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
@@ -1441,15 +1445,19 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>なければ</t>
+          <t>注意する</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>ない的假定型</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr"/>
+          <t>注意；警告</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>ちゅういする</t>
+        </is>
+      </c>
       <c r="E55" t="inlineStr"/>
     </row>
     <row r="56">
@@ -1458,20 +1466,16 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>なし</t>
+          <t>それですむ</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>没有，无</t>
+          <t>那样就行了，那样就解决了</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>あり-&gt;有</t>
-        </is>
-      </c>
+      <c r="E56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -1479,19 +1483,15 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>祝日</t>
+          <t>ああいう</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>节日，法定假日</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>しゅくじつ</t>
-        </is>
-      </c>
+          <t>那样的</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr"/>
     </row>
     <row r="58">
@@ -1500,19 +1500,15 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>教える</t>
+          <t>とは</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>教，告诉</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>おしえる</t>
-        </is>
-      </c>
+          <t>所谓...；竟然...</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr"/>
     </row>
     <row r="59">
@@ -1521,12 +1517,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>しゃべる</t>
+          <t>ことで</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>说话，聊天</t>
+          <t>通过...，因为...</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
@@ -1538,15 +1534,19 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>トップ</t>
+          <t>いつの間に</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>顶端，最高处</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr"/>
+          <t>不知不觉地</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>いつのまに</t>
+        </is>
+      </c>
       <c r="E60" t="inlineStr"/>
     </row>
     <row r="61">
@@ -1555,12 +1555,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>すごく</t>
+          <t>なければ</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>非常</t>
+          <t>如果不...的话</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>

--- a/READING/3_22_07.xlsx
+++ b/READING/3_22_07.xlsx
@@ -464,7 +464,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -485,58 +485,54 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>流れ</t>
+          <t>取り組む</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>流程，流逝</t>
+          <t>致力于，专心从事</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>ながれ</t>
+          <t>とりくむ</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>抑える</t>
+          <t>つまらない</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>胜过;击败</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>おさえる</t>
-        </is>
-      </c>
+          <t>无聊的</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>すなわち</t>
+          <t>おそらく</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>也就是说，换言之</t>
+          <t>大概，恐怕</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -544,16 +540,16 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>さっさと</t>
+          <t>みたいに</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>赶快地，迅速地</t>
+          <t>像...一样</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -561,16 +557,16 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>コツ</t>
+          <t>〜たとたんに</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>诀窍，窍门</t>
+          <t>刚一...就...</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -578,24 +574,20 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>まっすぐ</t>
+          <t>やみくもに</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>笔直地，直接地</t>
+          <t>盲目地，胡乱地</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>ちょくせつ-&gt;直接</t>
-        </is>
-      </c>
+      <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -603,113 +595,113 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>決まり文句</t>
+          <t>セール</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>口头禅，常用语，客套话</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>きまりもんく</t>
-        </is>
-      </c>
+          <t>甩卖，大减价</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>やっかいな</t>
+          <t>詰まる</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>麻烦的，棘手的</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>堵塞，塞满</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>つまる</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>取り組む</t>
+          <t>かなりある</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>致力于，专心从事</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>とりくむ</t>
-        </is>
-      </c>
+          <t>有很多</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>詰まる</t>
+          <t>やっかいな</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>堵塞，塞满</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>つまる</t>
-        </is>
-      </c>
+          <t>麻烦的，棘手的</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>セール</t>
+          <t>決まり文句</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>甩卖，大减价</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>口头禅，常用语，客套话</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>きまりもんく</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>かなりある</t>
+          <t>まっすぐ</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>有很多</t>
+          <t>笔直地，直接地</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>ちょくせつ-&gt;直接</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -717,12 +709,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>やみくもに</t>
+          <t>さっさと</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>盲目地，胡乱地</t>
+          <t>赶快地，迅速地</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -730,16 +722,16 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>〜となります</t>
+          <t>すなわち</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>规定…</t>
+          <t>也就是说，换言之</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -747,91 +739,103 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>〜たとたんに</t>
+          <t>抑える</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>刚一...就...</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>胜过;击败</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>おさえる</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>みたいに</t>
+          <t>見回る</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>像...一样</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>巡视，环视</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>みまわる</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>おそらく</t>
+          <t>といえば</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>大概，恐怕</t>
+          <t>说起...</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>たとえば→比如</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>つまらない</t>
+          <t>繰返する</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>无聊的</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
+          <t>重复</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>くりかえしする</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>無断</t>
+          <t>どんなに〜でも</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>擅自，私自</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>むだん</t>
-        </is>
-      </c>
+          <t>无论多么......也</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
     </row>
     <row r="22">
@@ -840,29 +844,33 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>まったく</t>
+          <t>得をする</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>完全，简直是</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
+          <t>获利，占便宜</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>とくをする</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>しっかり</t>
+          <t>押しつけ</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>好好地，牢固地</t>
+          <t>强加于人</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -870,33 +878,37 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>とにかく</t>
+          <t>流れ</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>总之，无论如何</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
+          <t>流程，流逝</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>ながれ</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>きちんと</t>
+          <t>どっぷり</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>好好地，整洁地</t>
+          <t>完全陷入</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -904,37 +916,33 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>親子</t>
+          <t>いったん</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>父母与子女，亲子</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>おやこ</t>
-        </is>
-      </c>
+          <t>一旦；暂时</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>〜ばよい</t>
+          <t>コツ</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>......就好了</t>
+          <t>诀窍，窍门</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -946,33 +954,29 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>見回る</t>
+          <t>〜となります</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>巡视，环视</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>みまわる</t>
-        </is>
-      </c>
+          <t>规定…</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>それくらい</t>
+          <t>まったく</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>那种程度</t>
+          <t>完全，简直是</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -984,12 +988,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ようとする</t>
+          <t>しっかり</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>正想要做...，试图做...</t>
+          <t>好好地，牢固地</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -997,36 +1001,44 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>どっぷり</t>
+          <t>親子</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>完全陷入</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr"/>
+          <t>父母与子女，亲子</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>おやこ</t>
+        </is>
+      </c>
       <c r="E31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>いったん</t>
+          <t>逃げ続ける</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>一旦；暂时</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr"/>
+          <t>持续逃跑</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>にげつづける</t>
+        </is>
+      </c>
       <c r="E32" t="inlineStr"/>
     </row>
     <row r="33">
@@ -1035,29 +1047,33 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>できるだけ</t>
+          <t>無断</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>尽可能地，尽量</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr"/>
+          <t>擅自，私自</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>むだん</t>
+        </is>
+      </c>
       <c r="E33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>押しつけ</t>
+          <t>〜ばよい</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>强加于人</t>
+          <t>......就好了</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
@@ -1069,33 +1085,29 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>得をする</t>
+          <t>できるだけ</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>获利，占便宜</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>とくをする</t>
-        </is>
-      </c>
+          <t>尽可能地，尽量</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>どんなに〜でも</t>
+          <t>とにかく</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>无论多么......也</t>
+          <t>总之，无论如何</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
@@ -1107,41 +1119,33 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>逃げ続ける</t>
+          <t>きちんと</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>持续逃跑</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>にげつづける</t>
-        </is>
-      </c>
+          <t>好好地，整洁地</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>といえば</t>
+          <t>ようとする</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>说起...</t>
+          <t>正想要做...，试图做...</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>たとえば→比如</t>
-        </is>
-      </c>
+      <c r="E38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1149,39 +1153,35 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>繰返する</t>
+          <t>それくらい</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>重复</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>くりかえしする</t>
-        </is>
-      </c>
+          <t>那种程度</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>なし</t>
+          <t>ほかの</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>没有，无</t>
+          <t>别的，其他的</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>あり-&gt;有</t>
+          <t>ほかり-&gt;其他的；除…之外，还有…</t>
         </is>
       </c>
     </row>
@@ -1191,19 +1191,15 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>少なくとも</t>
+          <t>ように</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>至少</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>すくなくとも</t>
-        </is>
-      </c>
+          <t>为了...；像...一样</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr"/>
     </row>
     <row r="42">
@@ -1212,12 +1208,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>このとおり</t>
+          <t>なければ</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>就照这样</t>
+          <t>如果不...的话</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
@@ -1229,15 +1225,19 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>なければ</t>
+          <t>いつの間に</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>ない的假定型</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr"/>
+          <t>不知不觉地</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>いつのまに</t>
+        </is>
+      </c>
       <c r="E43" t="inlineStr"/>
     </row>
     <row r="44">
@@ -1246,12 +1246,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>しゃべる</t>
+          <t>ことで</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>说话，聊天</t>
+          <t>通过...，因为...</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
@@ -1263,19 +1263,15 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>祝日</t>
+          <t>とは</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>节日，法定假日</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>しゅくじつ</t>
-        </is>
-      </c>
+          <t>所谓...；竟然...</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr"/>
     </row>
     <row r="46">
@@ -1284,19 +1280,15 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>教える</t>
+          <t>ああいう</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>教，告诉</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>おしえる</t>
-        </is>
-      </c>
+          <t>那样的</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr"/>
     </row>
     <row r="47">
@@ -1305,12 +1297,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>すでに</t>
+          <t>それですむ</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>已经</t>
+          <t>那样就行了，那样就解决了</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
@@ -1322,15 +1314,19 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>トップ</t>
+          <t>注意する</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>顶端，最高处</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr"/>
+          <t>注意；警告</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>ちゅういする</t>
+        </is>
+      </c>
       <c r="E48" t="inlineStr"/>
     </row>
     <row r="49">
@@ -1339,12 +1335,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>すごく</t>
+          <t>たがる</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>非常</t>
+          <t>（第三方）想要...</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
@@ -1352,24 +1348,20 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>ほかの</t>
+          <t>だと</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>别的，其他的</t>
+          <t>如果…的话,</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>ほかり-&gt;其他的；除…之外，还有…</t>
-        </is>
-      </c>
+      <c r="E50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -1377,15 +1369,19 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>なくす</t>
+          <t>祝日</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>弄丢，消除</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr"/>
+          <t>节日，法定假日</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>しゅくじつ</t>
+        </is>
+      </c>
       <c r="E51" t="inlineStr"/>
     </row>
     <row r="52">
@@ -1394,12 +1390,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>ように</t>
+          <t>なくす</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>为了...；像...一样</t>
+          <t>弄丢，消除</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
@@ -1411,12 +1407,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>だと</t>
+          <t>すごく</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>如果…的话,</t>
+          <t>非常</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
@@ -1428,12 +1424,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>たがる</t>
+          <t>トップ</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>（第三方）想要...</t>
+          <t>顶端，最高处</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
@@ -1445,19 +1441,15 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>注意する</t>
+          <t>すでに</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>注意；警告</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>ちゅういする</t>
-        </is>
-      </c>
+          <t>已经</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr"/>
     </row>
     <row r="56">
@@ -1466,15 +1458,19 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>それですむ</t>
+          <t>教える</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>那样就行了，那样就解决了</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr"/>
+          <t>教，告诉</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>おしえる</t>
+        </is>
+      </c>
       <c r="E56" t="inlineStr"/>
     </row>
     <row r="57">
@@ -1483,12 +1479,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ああいう</t>
+          <t>しゃべる</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>那样的</t>
+          <t>说话，聊天</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
@@ -1500,12 +1496,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>とは</t>
+          <t>なければ</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>所谓...；竟然...</t>
+          <t>ない的假定型</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
@@ -1517,12 +1513,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ことで</t>
+          <t>このとおり</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>通过...，因为...</t>
+          <t>就照这样</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
@@ -1534,41 +1530,45 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>いつの間に</t>
+          <t>少なくとも</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>不知不觉地</t>
+          <t>至少</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>いつのまに</t>
+          <t>すくなくとも</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>なければ</t>
+          <t>なし</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>如果不...的话</t>
+          <t>没有，无</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
-      <c r="E61" t="inlineStr"/>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>あり-&gt;有</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>

--- a/READING/3_22_07.xlsx
+++ b/READING/3_22_07.xlsx
@@ -464,58 +464,54 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>検討</t>
+          <t>やみくもに</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>讨论，研究</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>けんとう</t>
-        </is>
-      </c>
+          <t>盲目地，胡乱地</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>取り組む</t>
+          <t>まっすぐ</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>致力于，专心从事</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>とりくむ</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
+          <t>笔直地，直接地</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>ちょくせつ-&gt;直接</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>つまらない</t>
+          <t>〜たとたんに</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>无聊的</t>
+          <t>刚一...就...</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -523,16 +519,16 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>おそらく</t>
+          <t>すなわち</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>大概，恐怕</t>
+          <t>也就是说，换言之</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -540,33 +536,37 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>みたいに</t>
+          <t>取り組む</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>像...一样</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>致力于，专心从事</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>とりくむ</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>〜たとたんに</t>
+          <t>さっさと</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>刚一...就...</t>
+          <t>赶快地，迅速地</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -574,16 +574,16 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>やみくもに</t>
+          <t>つまらない</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>盲目地，胡乱地</t>
+          <t>无聊的</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -591,71 +591,75 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>セール</t>
+          <t>詰まる</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>甩卖，大减价</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>堵塞，塞满</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>つまる</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>詰まる</t>
+          <t>やっかいな</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>堵塞，塞满</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>つまる</t>
-        </is>
-      </c>
+          <t>麻烦的，棘手的</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>かなりある</t>
+          <t>決まり文句</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>有很多</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>口头禅，常用语，客套话</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>きまりもんく</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>やっかいな</t>
+          <t>まったく</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>麻烦的，棘手的</t>
+          <t>完全，简直是</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -663,23 +667,19 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>決まり文句</t>
+          <t>かなりある</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>口头禅，常用语，客套话</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>きまりもんく</t>
-        </is>
-      </c>
+          <t>有很多</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
     </row>
     <row r="14">
@@ -688,33 +688,33 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>まっすぐ</t>
+          <t>抑える</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>笔直地，直接地</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>ちょくせつ-&gt;直接</t>
-        </is>
-      </c>
+          <t>胜过;击败</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>おさえる</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>さっさと</t>
+          <t>押しつけ</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>赶快地，迅速地</t>
+          <t>强加于人</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -726,12 +726,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>すなわち</t>
+          <t>みたいに</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>也就是说，换言之</t>
+          <t>像...一样</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -743,82 +743,74 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>抑える</t>
+          <t>おそらく</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>胜过;击败</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>おさえる</t>
-        </is>
-      </c>
+          <t>大概，恐怕</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>見回る</t>
+          <t>検討</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>巡视，环视</t>
+          <t>讨论，研究</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>みまわる</t>
+          <t>けんとう</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>といえば</t>
+          <t>得をする</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>说起...</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>たとえば→比如</t>
-        </is>
-      </c>
+          <t>获利，占便宜</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>とくをする</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>繰返する</t>
+          <t>セール</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>重复</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>くりかえしする</t>
-        </is>
-      </c>
+          <t>甩卖，大减价</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
     </row>
     <row r="21">
@@ -827,12 +819,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>どんなに〜でも</t>
+          <t>コツ</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>无论多么......也</t>
+          <t>诀窍，窍门</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -840,41 +832,41 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>得をする</t>
+          <t>どんなに〜でも</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>获利，占便宜</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>とくをする</t>
-        </is>
-      </c>
+          <t>无论多么......也</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>押しつけ</t>
+          <t>といえば</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>强加于人</t>
+          <t>说起...</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>たとえば→比如</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -903,12 +895,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>どっぷり</t>
+          <t>できるだけ</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>完全陷入</t>
+          <t>尽可能地，尽量</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -920,32 +912,40 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>いったん</t>
+          <t>見回る</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>一旦；暂时</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
+          <t>巡视，环视</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>みまわる</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>コツ</t>
+          <t>繰返する</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>诀窍，窍门</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
+          <t>重复</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>くりかえしする</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr"/>
     </row>
     <row r="28">
@@ -954,12 +954,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>〜となります</t>
+          <t>いったん</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>规定…</t>
+          <t>一旦；暂时</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -971,12 +971,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>まったく</t>
+          <t>どっぷり</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>完全，简直是</t>
+          <t>完全陷入</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -984,16 +984,16 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>しっかり</t>
+          <t>〜となります</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>好好地，牢固地</t>
+          <t>规定…</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -1001,23 +1001,19 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>親子</t>
+          <t>それくらい</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>父母与子女，亲子</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>おやこ</t>
-        </is>
-      </c>
+          <t>那种程度</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
     </row>
     <row r="32">
@@ -1026,19 +1022,15 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>逃げ続ける</t>
+          <t>とにかく</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>持续逃跑</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>にげつづける</t>
-        </is>
-      </c>
+          <t>总之，无论如何</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
     </row>
     <row r="33">
@@ -1047,19 +1039,15 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>無断</t>
+          <t>ないといけない</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>擅自，私自</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>むだん</t>
-        </is>
-      </c>
+          <t>不得不...，必须...</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr"/>
     </row>
     <row r="34">
@@ -1068,12 +1056,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>〜ばよい</t>
+          <t>しっかり</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>......就好了</t>
+          <t>好好地，牢固地</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
@@ -1081,19 +1069,23 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>できるだけ</t>
+          <t>親子</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>尽可能地，尽量</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr"/>
+          <t>父母与子女，亲子</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>おやこ</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr"/>
     </row>
     <row r="36">
@@ -1102,15 +1094,19 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>とにかく</t>
+          <t>無断</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>总之，无论如何</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr"/>
+          <t>擅自，私自</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>むだん</t>
+        </is>
+      </c>
       <c r="E36" t="inlineStr"/>
     </row>
     <row r="37">
@@ -1119,12 +1115,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>きちんと</t>
+          <t>〜ばよい</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>好好地，整洁地</t>
+          <t>......就好了</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
@@ -1136,33 +1132,41 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>ようとする</t>
+          <t>なし</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>正想要做...，试图做...</t>
+          <t>没有，无</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>あり-&gt;有</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>それくらい</t>
+          <t>ほかの</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>那种程度</t>
+          <t>别的，其他的</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>ほかり-&gt;其他的；除…之外，还有…</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -1170,33 +1174,33 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>ほかの</t>
+          <t>逃げ続ける</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>别的，其他的</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>ほかり-&gt;其他的；除…之外，还有…</t>
-        </is>
-      </c>
+          <t>持续逃跑</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>にげつづける</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>ように</t>
+          <t>ようとする</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>为了...；像...一样</t>
+          <t>正想要做...，试图做...</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
@@ -1204,16 +1208,16 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>なければ</t>
+          <t>きちんと</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>如果不...的话</t>
+          <t>好好地，整洁地</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
@@ -1225,17 +1229,17 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>いつの間に</t>
+          <t>教える</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>不知不觉地</t>
+          <t>教，告诉</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>いつのまに</t>
+          <t>おしえる</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
@@ -1246,12 +1250,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>ことで</t>
+          <t>すでに</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>通过...，因为...</t>
+          <t>已经</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
@@ -1263,12 +1267,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>とは</t>
+          <t>なければ</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>所谓...；竟然...</t>
+          <t>如果不...的话</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
@@ -1280,15 +1284,19 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>ああいう</t>
+          <t>いつの間に</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>那样的</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr"/>
+          <t>不知不觉地</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>いつのまに</t>
+        </is>
+      </c>
       <c r="E46" t="inlineStr"/>
     </row>
     <row r="47">
@@ -1297,12 +1305,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>それですむ</t>
+          <t>ことで</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>那样就行了，那样就解决了</t>
+          <t>通过...，因为...</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
@@ -1314,19 +1322,15 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>注意する</t>
+          <t>とは</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>注意；警告</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>ちゅういする</t>
-        </is>
-      </c>
+          <t>所谓...；竟然...</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr"/>
     </row>
     <row r="49">
@@ -1335,12 +1339,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>たがる</t>
+          <t>ああいう</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>（第三方）想要...</t>
+          <t>那样的</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
@@ -1352,12 +1356,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>だと</t>
+          <t>それですむ</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>如果…的话,</t>
+          <t>那样就行了，那样就解决了</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
@@ -1390,12 +1394,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>なくす</t>
+          <t>しゃべる</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>弄丢，消除</t>
+          <t>说话，聊天</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
@@ -1407,15 +1411,19 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>すごく</t>
+          <t>注意する</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>非常</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr"/>
+          <t>注意；警告</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>ちゅういする</t>
+        </is>
+      </c>
       <c r="E53" t="inlineStr"/>
     </row>
     <row r="54">
@@ -1441,12 +1449,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>すでに</t>
+          <t>なければ</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>已经</t>
+          <t>ない的假定型</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
@@ -1458,19 +1466,15 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>教える</t>
+          <t>このとおり</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>教，告诉</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>おしえる</t>
-        </is>
-      </c>
+          <t>就照这样</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr"/>
     </row>
     <row r="57">
@@ -1479,15 +1483,19 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>しゃべる</t>
+          <t>少なくとも</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>说话，聊天</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr"/>
+          <t>至少</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>すくなくとも</t>
+        </is>
+      </c>
       <c r="E57" t="inlineStr"/>
     </row>
     <row r="58">
@@ -1496,12 +1504,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>なければ</t>
+          <t>すごく</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>ない的假定型</t>
+          <t>非常</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
@@ -1513,12 +1521,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>このとおり</t>
+          <t>ように</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>就照这样</t>
+          <t>为了...；像...一样</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
@@ -1530,54 +1538,46 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>少なくとも</t>
+          <t>なくす</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>至少</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>すくなくとも</t>
-        </is>
-      </c>
+          <t>弄丢，消除</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>なし</t>
+          <t>たがる</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>没有，无</t>
+          <t>（第三方）想要...</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>あり-&gt;有</t>
-        </is>
-      </c>
+      <c r="E61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>ないといけない</t>
+          <t>だと</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>不得不...，必须...</t>
+          <t>如果…的话,</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>

--- a/READING/3_22_07.xlsx
+++ b/READING/3_22_07.xlsx
@@ -464,70 +464,62 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>検討</t>
+          <t>やみくもに</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>讨论，研究</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>けんとう</t>
-        </is>
-      </c>
+          <t>盲目地，胡乱地</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>流れ</t>
+          <t>まっすぐ</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>流程，流逝</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>ながれ</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
+          <t>笔直地，直接地</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>ちょくせつ-&gt;直接</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>抑える</t>
+          <t>〜たとたんに</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>胜过;击败</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>おさえる</t>
-        </is>
-      </c>
+          <t>刚一...就...</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -544,33 +536,37 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>さっさと</t>
+          <t>取り組む</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>赶快地，迅速地</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>致力于，专心从事</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>とりくむ</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>コツ</t>
+          <t>さっさと</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>诀窍，窍门</t>
+          <t>赶快地，迅速地</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -578,49 +574,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>まっすぐ</t>
+          <t>つまらない</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>笔直地，直接地</t>
+          <t>无聊的</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>ちょくせつ-&gt;直接</t>
-        </is>
-      </c>
+      <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>決まり文句</t>
+          <t>詰まる</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>口头禅，常用语，客套话</t>
+          <t>堵塞，塞满</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>きまりもんく</t>
+          <t>つまる</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -637,58 +629,54 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>取り組む</t>
+          <t>決まり文句</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>致力于，专心从事</t>
+          <t>口头禅，常用语，客套话</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>とりくむ</t>
+          <t>きまりもんく</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>詰まる</t>
+          <t>まったく</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>堵塞，塞满</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>つまる</t>
-        </is>
-      </c>
+          <t>完全，简直是</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>セール</t>
+          <t>かなりある</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>甩卖，大减价</t>
+          <t>有很多</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -696,33 +684,37 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>かなりある</t>
+          <t>抑える</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>有很多</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>胜过;击败</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>おさえる</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>やみくもに</t>
+          <t>押しつけ</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>盲目地，胡乱地</t>
+          <t>强加于人</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -730,16 +722,16 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>〜となります</t>
+          <t>みたいに</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>规定…</t>
+          <t>像...一样</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -747,16 +739,16 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>〜たとたんに</t>
+          <t>おそらく</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>刚一...就...</t>
+          <t>大概，恐怕</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -764,19 +756,23 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>みたいに</t>
+          <t>検討</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>像...一样</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>讨论，研究</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>けんとう</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr"/>
     </row>
     <row r="19">
@@ -785,15 +781,19 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>おそらく</t>
+          <t>得をする</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>大概，恐怕</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>获利，占便宜</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>とくをする</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr"/>
     </row>
     <row r="20">
@@ -802,12 +802,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>つまらない</t>
+          <t>セール</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>无聊的</t>
+          <t>甩卖，大减价</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -815,37 +815,33 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>無断</t>
+          <t>コツ</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>擅自，私自</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>むだん</t>
-        </is>
-      </c>
+          <t>诀窍，窍门</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>まったく</t>
+          <t>どんなに〜でも</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>完全，简直是</t>
+          <t>无论多么......也</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -853,50 +849,58 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>しっかり</t>
+          <t>といえば</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>好好地，牢固地</t>
+          <t>说起...</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>たとえば→比如</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>とにかく</t>
+          <t>流れ</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>总之，无论如何</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
+          <t>流程，流逝</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>ながれ</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>きちんと</t>
+          <t>できるだけ</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>好好地，整洁地</t>
+          <t>尽可能地，尽量</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -904,40 +908,44 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>親子</t>
+          <t>見回る</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>父母与子女，亲子</t>
+          <t>巡视，环视</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>おやこ</t>
+          <t>みまわる</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>〜ばよい</t>
+          <t>繰返する</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>......就好了</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
+          <t>重复</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>くりかえしする</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr"/>
     </row>
     <row r="28">
@@ -946,33 +954,29 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>見回る</t>
+          <t>いったん</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>巡视，环视</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>みまわる</t>
-        </is>
-      </c>
+          <t>一旦；暂时</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>それくらい</t>
+          <t>どっぷり</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>那种程度</t>
+          <t>完全陷入</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -980,16 +984,16 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ようとする</t>
+          <t>〜となります</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>正想要做...，试图做...</t>
+          <t>规定…</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -1001,12 +1005,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>どっぷり</t>
+          <t>それくらい</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>完全陷入</t>
+          <t>那种程度</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -1014,16 +1018,16 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>いったん</t>
+          <t>とにかく</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>一旦；暂时</t>
+          <t>总之，无论如何</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -1035,12 +1039,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>できるだけ</t>
+          <t>ないといけない</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>尽可能地，尽量</t>
+          <t>不得不...，必须...</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -1048,16 +1052,16 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>押しつけ</t>
+          <t>しっかり</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>强加于人</t>
+          <t>好好地，牢固地</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
@@ -1065,40 +1069,44 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>得をする</t>
+          <t>親子</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>获利，占便宜</t>
+          <t>父母与子女，亲子</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>とくをする</t>
+          <t>おやこ</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>どんなに〜でも</t>
+          <t>無断</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>无论多么......也</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr"/>
+          <t>擅自，私自</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>むだん</t>
+        </is>
+      </c>
       <c r="E36" t="inlineStr"/>
     </row>
     <row r="37">
@@ -1107,117 +1115,109 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>逃げ続ける</t>
+          <t>〜ばよい</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>持续逃跑</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>にげつづける</t>
-        </is>
-      </c>
+          <t>......就好了</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>といえば</t>
+          <t>なし</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>说起...</t>
+          <t>没有，无</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>たとえば→比如</t>
+          <t>あり-&gt;有</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>繰返する</t>
+          <t>ほかの</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>重复</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>くりかえしする</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr"/>
+          <t>别的，其他的</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>ほかり-&gt;其他的；除…之外，还有…</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>なし</t>
+          <t>逃げ続ける</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>没有，无</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>あり-&gt;有</t>
-        </is>
-      </c>
+          <t>持续逃跑</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>にげつづける</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>少なくとも</t>
+          <t>ようとする</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>至少</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>すくなくとも</t>
-        </is>
-      </c>
+          <t>正想要做...，试图做...</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>このとおり</t>
+          <t>きちんと</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>就照这样</t>
+          <t>好好地，整洁地</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
@@ -1229,15 +1229,19 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>なければ</t>
+          <t>教える</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>ない的假定型</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr"/>
+          <t>教，告诉</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>おしえる</t>
+        </is>
+      </c>
       <c r="E43" t="inlineStr"/>
     </row>
     <row r="44">
@@ -1246,12 +1250,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>しゃべる</t>
+          <t>すでに</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>说话，聊天</t>
+          <t>已经</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
@@ -1263,19 +1267,15 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>祝日</t>
+          <t>なければ</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>节日，法定假日</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>しゅくじつ</t>
-        </is>
-      </c>
+          <t>如果不...的话</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr"/>
     </row>
     <row r="46">
@@ -1284,17 +1284,17 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>教える</t>
+          <t>いつの間に</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>教，告诉</t>
+          <t>不知不觉地</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>おしえる</t>
+          <t>いつのまに</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
@@ -1305,12 +1305,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>すでに</t>
+          <t>ことで</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>已经</t>
+          <t>通过...，因为...</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
@@ -1322,12 +1322,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>トップ</t>
+          <t>とは</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>顶端，最高处</t>
+          <t>所谓...；竟然...</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
@@ -1339,12 +1339,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>すごく</t>
+          <t>ああいう</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>非常</t>
+          <t>那样的</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
@@ -1352,24 +1352,20 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>ほかの</t>
+          <t>それですむ</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>别的，其他的</t>
+          <t>那样就行了，那样就解决了</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>ほかり-&gt;其他的；除…之外，还有…</t>
-        </is>
-      </c>
+      <c r="E50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -1377,15 +1373,19 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>なくす</t>
+          <t>祝日</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>弄丢，消除</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr"/>
+          <t>节日，法定假日</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>しゅくじつ</t>
+        </is>
+      </c>
       <c r="E51" t="inlineStr"/>
     </row>
     <row r="52">
@@ -1394,12 +1394,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>ように</t>
+          <t>しゃべる</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>为了...；像...一样</t>
+          <t>说话，聊天</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
@@ -1411,15 +1411,19 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>だと</t>
+          <t>注意する</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>如果…的话,</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr"/>
+          <t>注意；警告</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>ちゅういする</t>
+        </is>
+      </c>
       <c r="E53" t="inlineStr"/>
     </row>
     <row r="54">
@@ -1428,12 +1432,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>たがる</t>
+          <t>トップ</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>（第三方）想要...</t>
+          <t>顶端，最高处</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
@@ -1445,19 +1449,15 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>注意する</t>
+          <t>なければ</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>注意；警告</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>ちゅういする</t>
-        </is>
-      </c>
+          <t>ない的假定型</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr"/>
     </row>
     <row r="56">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>それですむ</t>
+          <t>このとおり</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>那样就行了，那样就解决了</t>
+          <t>就照这样</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
@@ -1483,15 +1483,19 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ああいう</t>
+          <t>少なくとも</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>那样的</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr"/>
+          <t>至少</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>すくなくとも</t>
+        </is>
+      </c>
       <c r="E57" t="inlineStr"/>
     </row>
     <row r="58">
@@ -1500,12 +1504,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>とは</t>
+          <t>すごく</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>所谓...；竟然...</t>
+          <t>非常</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
@@ -1517,12 +1521,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ことで</t>
+          <t>ように</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>通过...，因为...</t>
+          <t>为了...；像...一样</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
@@ -1534,19 +1538,15 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>いつの間に</t>
+          <t>なくす</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>不知不觉地</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>いつのまに</t>
-        </is>
-      </c>
+          <t>弄丢，消除</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr"/>
     </row>
     <row r="61">
@@ -1555,12 +1555,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>なければ</t>
+          <t>たがる</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>如果不...的话</t>
+          <t>（第三方）想要...</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
@@ -1572,12 +1572,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>ないといけない</t>
+          <t>だと</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>不得不...，必须...</t>
+          <t>如果…的话,</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>

--- a/READING/3_22_07.xlsx
+++ b/READING/3_22_07.xlsx
@@ -464,62 +464,70 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>やみくもに</t>
+          <t>検討</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>盲目地，胡乱地</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
+          <t>讨论，研究</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>けんとう</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>まっすぐ</t>
+          <t>流れ</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>笔直地，直接地</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>ちょくせつ-&gt;直接</t>
-        </is>
-      </c>
+          <t>流程，流逝</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>ながれ</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>〜たとたんに</t>
+          <t>抑える</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>刚一...就...</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>胜过;击败</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>おさえる</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -536,37 +544,33 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>取り組む</t>
+          <t>さっさと</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>致力于，专心从事</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>とりくむ</t>
-        </is>
-      </c>
+          <t>赶快地，迅速地</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>さっさと</t>
+          <t>コツ</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>赶快地，迅速地</t>
+          <t>诀窍，窍门</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -574,45 +578,49 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>つまらない</t>
+          <t>まっすぐ</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>无聊的</t>
+          <t>笔直地，直接地</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>ちょくせつ-&gt;直接</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>詰まる</t>
+          <t>決まり文句</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>堵塞，塞满</t>
+          <t>口头禅，常用语，客套话</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>つまる</t>
+          <t>きまりもんく</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -629,54 +637,58 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>決まり文句</t>
+          <t>取り組む</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>口头禅，常用语，客套话</t>
+          <t>致力于，专心从事</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>きまりもんく</t>
+          <t>とりくむ</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>まったく</t>
+          <t>詰まる</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>完全，简直是</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>堵塞，塞满</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>つまる</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>かなりある</t>
+          <t>セール</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>有很多</t>
+          <t>甩卖，大减价</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -684,37 +696,33 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>抑える</t>
+          <t>かなりある</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>胜过;击败</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>おさえる</t>
-        </is>
-      </c>
+          <t>有很多</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>押しつけ</t>
+          <t>やみくもに</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>强加于人</t>
+          <t>盲目地，胡乱地</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -722,16 +730,16 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>みたいに</t>
+          <t>〜となります</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>像...一样</t>
+          <t>规定…</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -739,16 +747,16 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>おそらく</t>
+          <t>〜たとたんに</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>大概，恐怕</t>
+          <t>刚一...就...</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -756,23 +764,19 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>検討</t>
+          <t>みたいに</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>讨论，研究</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>けんとう</t>
-        </is>
-      </c>
+          <t>像...一样</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
     </row>
     <row r="19">
@@ -781,19 +785,15 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>得をする</t>
+          <t>おそらく</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>获利，占便宜</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>とくをする</t>
-        </is>
-      </c>
+          <t>大概，恐怕</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
     </row>
     <row r="20">
@@ -802,12 +802,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>セール</t>
+          <t>つまらない</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>甩卖，大减价</t>
+          <t>无聊的</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -815,33 +815,37 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>コツ</t>
+          <t>無断</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>诀窍，窍门</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
+          <t>擅自，私自</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>むだん</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>どんなに〜でも</t>
+          <t>まったく</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>无论多么......也</t>
+          <t>完全，简直是</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -849,58 +853,50 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>といえば</t>
+          <t>しっかり</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>说起...</t>
+          <t>好好地，牢固地</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>たとえば→比如</t>
-        </is>
-      </c>
+      <c r="E23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>流れ</t>
+          <t>とにかく</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>流程，流逝</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>ながれ</t>
-        </is>
-      </c>
+          <t>总之，无论如何</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>できるだけ</t>
+          <t>きちんと</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>尽可能地，尽量</t>
+          <t>好好地，整洁地</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -908,44 +904,40 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>見回る</t>
+          <t>親子</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>巡视，环视</t>
+          <t>父母与子女，亲子</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>みまわる</t>
+          <t>おやこ</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>繰返する</t>
+          <t>〜ばよい</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>重复</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>くりかえしする</t>
-        </is>
-      </c>
+          <t>......就好了</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr"/>
     </row>
     <row r="28">
@@ -954,29 +946,33 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>いったん</t>
+          <t>見回る</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>一旦；暂时</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
+          <t>巡视，环视</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>みまわる</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>どっぷり</t>
+          <t>それくらい</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>完全陷入</t>
+          <t>那种程度</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -984,16 +980,16 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>〜となります</t>
+          <t>ようとする</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>规定…</t>
+          <t>正想要做...，试图做...</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -1005,12 +1001,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>それくらい</t>
+          <t>どっぷり</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>那种程度</t>
+          <t>完全陷入</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -1018,16 +1014,16 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>とにかく</t>
+          <t>いったん</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>总之，无论如何</t>
+          <t>一旦；暂时</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -1039,12 +1035,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>ないといけない</t>
+          <t>できるだけ</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>不得不...，必须...</t>
+          <t>尽可能地，尽量</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -1052,16 +1048,16 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>しっかり</t>
+          <t>押しつけ</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>好好地，牢固地</t>
+          <t>强加于人</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
@@ -1069,44 +1065,40 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>親子</t>
+          <t>得をする</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>父母与子女，亲子</t>
+          <t>获利，占便宜</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>おやこ</t>
+          <t>とくをする</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>無断</t>
+          <t>どんなに〜でも</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>擅自，私自</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>むだん</t>
-        </is>
-      </c>
+          <t>无论多么......也</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr"/>
     </row>
     <row r="37">
@@ -1115,109 +1107,117 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>〜ばよい</t>
+          <t>逃げ続ける</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>......就好了</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr"/>
+          <t>持续逃跑</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>にげつづける</t>
+        </is>
+      </c>
       <c r="E37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>なし</t>
+          <t>といえば</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>没有，无</t>
+          <t>说起...</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>あり-&gt;有</t>
+          <t>たとえば→比如</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>ほかの</t>
+          <t>繰返する</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>别的，其他的</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>ほかり-&gt;其他的；除…之外，还有…</t>
-        </is>
-      </c>
+          <t>重复</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>くりかえしする</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>逃げ続ける</t>
+          <t>なし</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>持续逃跑</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>にげつづける</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr"/>
+          <t>没有，无</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>あり-&gt;有</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>ようとする</t>
+          <t>少なくとも</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>正想要做...，试图做...</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr"/>
+          <t>至少</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>すくなくとも</t>
+        </is>
+      </c>
       <c r="E41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>きちんと</t>
+          <t>このとおり</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>好好地，整洁地</t>
+          <t>就照这样</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
@@ -1229,19 +1229,15 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>教える</t>
+          <t>なければ</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>教，告诉</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>おしえる</t>
-        </is>
-      </c>
+          <t>ない的假定型</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr"/>
     </row>
     <row r="44">
@@ -1250,12 +1246,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>すでに</t>
+          <t>しゃべる</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>已经</t>
+          <t>说话，聊天</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
@@ -1267,15 +1263,19 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>なければ</t>
+          <t>祝日</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>如果不...的话</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr"/>
+          <t>节日，法定假日</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>しゅくじつ</t>
+        </is>
+      </c>
       <c r="E45" t="inlineStr"/>
     </row>
     <row r="46">
@@ -1284,17 +1284,17 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>いつの間に</t>
+          <t>教える</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>不知不觉地</t>
+          <t>教，告诉</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>いつのまに</t>
+          <t>おしえる</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
@@ -1305,12 +1305,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>ことで</t>
+          <t>すでに</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>通过...，因为...</t>
+          <t>已经</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
@@ -1322,12 +1322,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>とは</t>
+          <t>トップ</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>所谓...；竟然...</t>
+          <t>顶端，最高处</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
@@ -1339,12 +1339,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>ああいう</t>
+          <t>すごく</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>那样的</t>
+          <t>非常</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
@@ -1352,20 +1352,24 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>それですむ</t>
+          <t>ほかの</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>那样就行了，那样就解决了</t>
+          <t>别的，其他的</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>ほかり-&gt;其他的；除…之外，还有…</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -1373,19 +1377,15 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>祝日</t>
+          <t>なくす</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>节日，法定假日</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>しゅくじつ</t>
-        </is>
-      </c>
+          <t>弄丢，消除</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr"/>
     </row>
     <row r="52">
@@ -1394,12 +1394,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>しゃべる</t>
+          <t>ように</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>说话，聊天</t>
+          <t>为了...；像...一样</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
@@ -1411,19 +1411,15 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>注意する</t>
+          <t>だと</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>注意；警告</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>ちゅういする</t>
-        </is>
-      </c>
+          <t>如果…的话,</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr"/>
     </row>
     <row r="54">
@@ -1432,12 +1428,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>トップ</t>
+          <t>たがる</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>顶端，最高处</t>
+          <t>（第三方）想要...</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
@@ -1449,15 +1445,19 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>なければ</t>
+          <t>注意する</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>ない的假定型</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr"/>
+          <t>注意；警告</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>ちゅういする</t>
+        </is>
+      </c>
       <c r="E55" t="inlineStr"/>
     </row>
     <row r="56">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>このとおり</t>
+          <t>それですむ</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>就照这样</t>
+          <t>那样就行了，那样就解决了</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
@@ -1483,19 +1483,15 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>少なくとも</t>
+          <t>ああいう</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>至少</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>すくなくとも</t>
-        </is>
-      </c>
+          <t>那样的</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr"/>
     </row>
     <row r="58">
@@ -1504,12 +1500,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>すごく</t>
+          <t>とは</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>非常</t>
+          <t>所谓...；竟然...</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
@@ -1521,12 +1517,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ように</t>
+          <t>ことで</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>为了...；像...一样</t>
+          <t>通过...，因为...</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
@@ -1538,15 +1534,19 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>なくす</t>
+          <t>いつの間に</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>弄丢，消除</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr"/>
+          <t>不知不觉地</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>いつのまに</t>
+        </is>
+      </c>
       <c r="E60" t="inlineStr"/>
     </row>
     <row r="61">
@@ -1555,12 +1555,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>たがる</t>
+          <t>なければ</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>（第三方）想要...</t>
+          <t>如果不...的话</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
@@ -1572,12 +1572,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>だと</t>
+          <t>ないといけない</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>如果…的话,</t>
+          <t>不得不...，必须...</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>

--- a/READING/3_22_07.xlsx
+++ b/READING/3_22_07.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E82"/>
+  <dimension ref="A1:E62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="2" max="2"/>
@@ -464,7 +464,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -506,12 +506,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>タネ</t>
+          <t>〜たとたんに</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>种子</t>
+          <t>刚一...就...</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -523,12 +523,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>押しつけ</t>
+          <t>すなわち</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>强加于人</t>
+          <t>也就是说，换言之</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -536,33 +536,37 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>〜たとたんに</t>
+          <t>取り組む</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>刚一...就...</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>致力于，专心从事</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>とりくむ</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>セール</t>
+          <t>さっさと</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>甩卖，大减价</t>
+          <t>赶快地，迅速地</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -570,16 +574,16 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>さっさと</t>
+          <t>つまらない</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>赶快地，迅速地</t>
+          <t>无聊的</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -587,37 +591,37 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>淋しい</t>
+          <t>詰まる</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>寂寞的</t>
+          <t>堵塞，塞满</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>さびしい</t>
+          <t>つまる</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>オリジナル</t>
+          <t>やっかいな</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>original；原型</t>
+          <t>麻烦的，棘手的</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -629,15 +633,19 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>そろいにくい</t>
+          <t>決まり文句</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>难以具备</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>口头禅，常用语，客套话</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>きまりもんく</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr"/>
     </row>
     <row r="12">
@@ -646,12 +654,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>つまらない</t>
+          <t>まったく</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>无聊的</t>
+          <t>完全，简直是</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -659,16 +667,16 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>いったん</t>
+          <t>かなりある</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>一旦；暂时</t>
+          <t>有很多</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -680,17 +688,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>詰まる</t>
+          <t>抑える</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>堵塞，塞满</t>
+          <t>胜过;击败</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>つまる</t>
+          <t>おさえる</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
@@ -701,12 +709,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>やっかいな</t>
+          <t>押しつけ</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>麻烦的，棘手的</t>
+          <t>强加于人</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -714,16 +722,16 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>かなりある</t>
+          <t>みたいに</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>有很多</t>
+          <t>像...一样</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -731,40 +739,40 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>繰返する</t>
+          <t>おそらく</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>重复</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>くりかえしする</t>
-        </is>
-      </c>
+          <t>大概，恐怕</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>みたいに</t>
+          <t>検討</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>像...一样</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>讨论，研究</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>けんとう</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr"/>
     </row>
     <row r="19">
@@ -773,15 +781,19 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>おそらく</t>
+          <t>得をする</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>大概，恐怕</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>获利，占便宜</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>とくをする</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr"/>
     </row>
     <row r="20">
@@ -790,19 +802,15 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>抑える</t>
+          <t>セール</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>胜过;击败</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>おさえる</t>
-        </is>
-      </c>
+          <t>甩卖，大减价</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
     </row>
     <row r="21">
@@ -811,19 +819,15 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>決まり文句</t>
+          <t>コツ</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>口头禅，常用语，客套话</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>きまりもんく</t>
-        </is>
-      </c>
+          <t>诀窍，窍门</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
     </row>
     <row r="22">
@@ -832,19 +836,15 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>取り組む</t>
+          <t>どんなに〜でも</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>致力于，专心从事</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>とりくむ</t>
-        </is>
-      </c>
+          <t>无论多么......也</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr"/>
     </row>
     <row r="23">
@@ -853,50 +853,54 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>すなわち</t>
+          <t>といえば</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>也就是说，换言之</t>
+          <t>说起...</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>たとえば→比如</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>見回る</t>
+          <t>流れ</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>巡视，环视</t>
+          <t>流程，流逝</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>みまわる</t>
+          <t>ながれ</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>ハサミ</t>
+          <t>できるだけ</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>剪刀</t>
+          <t>尽可能地，尽量</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -904,40 +908,44 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>検討</t>
+          <t>見回る</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>讨论，研究</t>
+          <t>巡视，环视</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>けんとう</t>
+          <t>みまわる</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>シリーズ</t>
+          <t>繰返する</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>series</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
+          <t>重复</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>くりかえしする</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr"/>
     </row>
     <row r="28">
@@ -946,12 +954,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>何でも</t>
+          <t>いったん</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>无论什么</t>
+          <t>一旦；暂时</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -963,12 +971,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ぜひ</t>
+          <t>どっぷり</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>一定</t>
+          <t>完全陷入</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -980,12 +988,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ことがある</t>
+          <t>〜となります</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>偶尔</t>
+          <t>规定…</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -997,12 +1005,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ショップ</t>
+          <t>それくらい</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>shop</t>
+          <t>那种程度</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -1010,16 +1018,16 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>ではあります</t>
+          <t>とにかく</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>是…</t>
+          <t>总之，无论如何</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -1027,16 +1035,16 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>間違い</t>
+          <t>ないといけない</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>错误的</t>
+          <t>不得不...，必须...</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -1044,16 +1052,16 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>ばよい</t>
+          <t>しっかり</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>…就可以</t>
+          <t>好好地，牢固地</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
@@ -1061,50 +1069,58 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>そろう</t>
+          <t>親子</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>齐全的</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr"/>
+          <t>父母与子女，亲子</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>おやこ</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>のみ</t>
+          <t>無断</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>仅仅</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr"/>
+          <t>擅自，私自</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>むだん</t>
+        </is>
+      </c>
       <c r="E36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>とにかく</t>
+          <t>〜ばよい</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>总之，无论如何</t>
+          <t>......就好了</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
@@ -1112,71 +1128,79 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>取り除く</t>
+          <t>なし</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>移除；消除</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>とりのぞく</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr"/>
+          <t>没有，无</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>あり-&gt;有</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>と思われがちです</t>
+          <t>ほかの</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>常常认为…</t>
+          <t>别的，其他的</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>ほかり-&gt;其他的；除…之外，还有…</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>一度</t>
+          <t>逃げ続ける</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>一次</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr"/>
+          <t>持续逃跑</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>にげつづける</t>
+        </is>
+      </c>
       <c r="E40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>どっぷり</t>
+          <t>ようとする</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>完全陷入</t>
+          <t>正想要做...，试图做...</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
@@ -1184,16 +1208,16 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>...ていく</t>
+          <t>きちんと</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>…持续下去</t>
+          <t>好好地，整洁地</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
@@ -1201,37 +1225,37 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>流れ</t>
+          <t>教える</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>流程，流逝</t>
+          <t>教，告诉</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>ながれ</t>
+          <t>おしえる</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>どんなに〜でも</t>
+          <t>すでに</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>无论多么......也</t>
+          <t>已经</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
@@ -1239,16 +1263,16 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>まったく</t>
+          <t>なければ</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>完全，简直是</t>
+          <t>如果不...的话</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
@@ -1256,33 +1280,37 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>〜となります</t>
+          <t>いつの間に</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>规定…</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr"/>
+          <t>不知不觉地</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>いつのまに</t>
+        </is>
+      </c>
       <c r="E46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>コツ</t>
+          <t>ことで</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>诀窍，窍门</t>
+          <t>通过...，因为...</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
@@ -1290,37 +1318,33 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>得をする</t>
+          <t>とは</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>获利，占便宜</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>とくをする</t>
-        </is>
-      </c>
+          <t>所谓...；竟然...</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>...のです</t>
+          <t>ああいう</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>因为</t>
+          <t>那样的</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
@@ -1328,92 +1352,92 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>といえば</t>
+          <t>それですむ</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>说起...</t>
+          <t>那样就行了，那样就解决了</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>たとえば→比如</t>
-        </is>
-      </c>
+      <c r="E50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>きちんと</t>
+          <t>祝日</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>好好地，整洁地</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr"/>
+          <t>节日，法定假日</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>しゅくじつ</t>
+        </is>
+      </c>
       <c r="E51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>逃げ続ける</t>
+          <t>しゃべる</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>持续逃跑</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>にげつづける</t>
-        </is>
-      </c>
+          <t>说话，聊天</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>〜ばよい</t>
+          <t>注意する</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>......就好了</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr"/>
+          <t>注意；警告</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>ちゅういする</t>
+        </is>
+      </c>
       <c r="E53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ようとする</t>
+          <t>トップ</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>正想要做...，试图做...</t>
+          <t>顶端，最高处</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
@@ -1421,37 +1445,33 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>親子</t>
+          <t>なければ</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>父母与子女，亲子</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>おやこ</t>
-        </is>
-      </c>
+          <t>ない的假定型</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>それくらい</t>
+          <t>このとおり</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>那种程度</t>
+          <t>就照这样</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
@@ -1459,28 +1479,28 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>無断</t>
+          <t>少なくとも</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>擅自，私自</t>
+          <t>至少</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>むだん</t>
+          <t>すくなくとも</t>
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
@@ -1497,37 +1517,33 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ほかの</t>
+          <t>ように</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>别的，其他的</t>
+          <t>为了...；像...一样</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>ほかり-&gt;其他的；除…之外，还有…</t>
-        </is>
-      </c>
+      <c r="E59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>できるだけ</t>
+          <t>なくす</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>尽可能地，尽量</t>
+          <t>弄丢，消除</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
@@ -1535,16 +1551,16 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>しっかり</t>
+          <t>たがる</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>好好地，牢固地</t>
+          <t>（第三方）想要...</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
@@ -1556,380 +1572,16 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>教える</t>
+          <t>だと</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>教，告诉</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>おしえる</t>
-        </is>
-      </c>
+          <t>如果…的话,</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" t="n">
-        <v>0</v>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>すでに</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>已经</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr"/>
-      <c r="E63" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" t="n">
-        <v>0</v>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>なし</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>没有，无</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr"/>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>あり-&gt;有</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="n">
-        <v>0</v>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>なければ</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>如果不...的话</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr"/>
-      <c r="E65" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" t="n">
-        <v>0</v>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>ないといけない</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>不得不...，必须...</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr"/>
-      <c r="E66" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" t="n">
-        <v>0</v>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>少なくとも</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>至少</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>すくなくとも</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" t="n">
-        <v>0</v>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>なければ</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>ない的假定型</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr"/>
-      <c r="E68" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" t="n">
-        <v>0</v>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>しゃべる</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>说话，聊天</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr"/>
-      <c r="E69" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" t="n">
-        <v>0</v>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>祝日</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>节日，法定假日</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>しゅくじつ</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" t="n">
-        <v>0</v>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>トップ</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>顶端，最高处</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr"/>
-      <c r="E71" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" t="n">
-        <v>0</v>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>たがる</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>（第三方）想要...</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr"/>
-      <c r="E72" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" t="n">
-        <v>0</v>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>ように</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>为了...；像...一样</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr"/>
-      <c r="E73" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" t="n">
-        <v>0</v>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>注意する</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>注意；警告</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>ちゅういする</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" t="n">
-        <v>0</v>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>それですむ</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>那样就行了，那样就解决了</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr"/>
-      <c r="E75" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" t="n">
-        <v>0</v>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>ああいう</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>那样的</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr"/>
-      <c r="E76" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" t="n">
-        <v>0</v>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>とは</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>所谓...；竟然...</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr"/>
-      <c r="E77" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" t="n">
-        <v>0</v>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>ことで</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>通过...，因为...</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr"/>
-      <c r="E78" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" t="n">
-        <v>0</v>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>いつの間に</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>不知不觉地</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>いつのまに</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" t="n">
-        <v>0</v>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>なくす</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>弄丢，消除</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr"/>
-      <c r="E80" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" t="n">
-        <v>0</v>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>だと</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>如果…的话,</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr"/>
-      <c r="E81" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" t="n">
-        <v>0</v>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>このとおり</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>就照这样</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr"/>
-      <c r="E82" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/READING/3_22_07.xlsx
+++ b/READING/3_22_07.xlsx
@@ -464,20 +464,24 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>やみくもに</t>
+          <t>まっすぐ</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>盲目地，胡乱地</t>
+          <t>笔直地，直接地</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>ちょくせつ-&gt;直接</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -485,20 +489,16 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>まっすぐ</t>
+          <t>やみくもに</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>笔直地，直接地</t>
+          <t>盲目地，胡乱地</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>ちょくせつ-&gt;直接</t>
-        </is>
-      </c>
+      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -506,12 +506,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>タネ</t>
+          <t>さっさと</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>种子</t>
+          <t>赶快地，迅速地</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -523,12 +523,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>押しつけ</t>
+          <t>セール</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>强加于人</t>
+          <t>甩卖，大减价</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -536,16 +536,16 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>〜たとたんに</t>
+          <t>つまらない</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>刚一...就...</t>
+          <t>无聊的</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -553,16 +553,16 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>セール</t>
+          <t>押しつけ</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>甩卖，大减价</t>
+          <t>强加于人</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -570,16 +570,16 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>さっさと</t>
+          <t>タネ</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>赶快地，迅速地</t>
+          <t>种子</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -591,19 +591,15 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>淋しい</t>
+          <t>オリジナル</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>寂寞的</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>さびしい</t>
-        </is>
-      </c>
+          <t>original；原型</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
@@ -612,12 +608,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>オリジナル</t>
+          <t>そろいにくい</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>original；原型</t>
+          <t>难以具备</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -629,15 +625,19 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>そろいにくい</t>
+          <t>淋しい</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>难以具备</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>寂寞的</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>さびしい</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr"/>
     </row>
     <row r="12">
@@ -646,12 +646,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>つまらない</t>
+          <t>〜たとたんに</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>无聊的</t>
+          <t>刚一...就...</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -659,7 +659,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -718,12 +718,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>かなりある</t>
+          <t>おそらく</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>有很多</t>
+          <t>大概，恐怕</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -735,17 +735,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>繰返する</t>
+          <t>抑える</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>重复</t>
+          <t>胜过;击败</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>くりかえしする</t>
+          <t>おさえる</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
@@ -756,12 +756,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>みたいに</t>
+          <t>かなりある</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>像...一样</t>
+          <t>有很多</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -773,15 +773,19 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>おそらく</t>
+          <t>繰返する</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>大概，恐怕</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>重复</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>くりかえしする</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr"/>
     </row>
     <row r="20">
@@ -790,19 +794,15 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>抑える</t>
+          <t>みたいに</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>胜过;击败</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>おさえる</t>
-        </is>
-      </c>
+          <t>像...一样</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
     </row>
     <row r="21">
@@ -832,19 +832,15 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>取り組む</t>
+          <t>ハサミ</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>致力于，专心从事</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>とりくむ</t>
-        </is>
-      </c>
+          <t>剪刀</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr"/>
     </row>
     <row r="23">
@@ -870,17 +866,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>見回る</t>
+          <t>検討</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>巡视，环视</t>
+          <t>讨论，研究</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>みまわる</t>
+          <t>けんとう</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
@@ -891,12 +887,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>ハサミ</t>
+          <t>シリーズ</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>剪刀</t>
+          <t>series</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -908,17 +904,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>検討</t>
+          <t>取り組む</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>讨论，研究</t>
+          <t>致力于，专心从事</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>けんとう</t>
+          <t>とりくむ</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
@@ -929,15 +925,19 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>シリーズ</t>
+          <t>見回る</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>series</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
+          <t>巡视，环视</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>みまわる</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr"/>
     </row>
     <row r="28">
@@ -946,12 +946,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>何でも</t>
+          <t>のみ</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>无论什么</t>
+          <t>仅仅</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -963,12 +963,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ぜひ</t>
+          <t>とにかく</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>一定</t>
+          <t>总之，无论如何</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -980,12 +980,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ことがある</t>
+          <t>と思われがちです</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>偶尔</t>
+          <t>常常认为…</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -997,12 +997,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ショップ</t>
+          <t>何でも</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>shop</t>
+          <t>无论什么</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -1014,15 +1014,19 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>ではあります</t>
+          <t>取り除く</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>是…</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr"/>
+          <t>移除；消除</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>とりのぞく</t>
+        </is>
+      </c>
       <c r="E32" t="inlineStr"/>
     </row>
     <row r="33">
@@ -1031,12 +1035,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>間違い</t>
+          <t>ぜひ</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>错误的</t>
+          <t>一定</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -1048,12 +1052,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>ばよい</t>
+          <t>ことがある</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>…就可以</t>
+          <t>偶尔</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
@@ -1065,12 +1069,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>そろう</t>
+          <t>ショップ</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>齐全的</t>
+          <t>shop</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
@@ -1082,12 +1086,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>のみ</t>
+          <t>ではあります</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>仅仅</t>
+          <t>是…</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
@@ -1099,12 +1103,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>とにかく</t>
+          <t>間違い</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>总之，无论如何</t>
+          <t>错误的</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
@@ -1116,19 +1120,15 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>取り除く</t>
+          <t>そろう</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>移除；消除</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>とりのぞく</t>
-        </is>
-      </c>
+          <t>齐全的</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr"/>
     </row>
     <row r="39">
@@ -1137,12 +1137,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>と思われがちです</t>
+          <t>ばよい</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>常常认为…</t>
+          <t>…就可以</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
@@ -1154,12 +1154,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>一度</t>
+          <t>どんなに〜でも</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>一次</t>
+          <t>无论多么......也</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
@@ -1171,12 +1171,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>どっぷり</t>
+          <t>まったく</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>完全陷入</t>
+          <t>完全，简直是</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>...ていく</t>
+          <t>〜となります</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>…持续下去</t>
+          <t>规定…</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
@@ -1205,19 +1205,15 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>流れ</t>
+          <t>コツ</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>流程，流逝</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>ながれ</t>
-        </is>
-      </c>
+          <t>诀窍，窍门</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr"/>
     </row>
     <row r="44">
@@ -1226,15 +1222,19 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>どんなに〜でも</t>
+          <t>得をする</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>无论多么......也</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr"/>
+          <t>获利，占便宜</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>とくをする</t>
+        </is>
+      </c>
       <c r="E44" t="inlineStr"/>
     </row>
     <row r="45">
@@ -1243,12 +1243,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>まったく</t>
+          <t>...のです</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>完全，简直是</t>
+          <t>因为</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
@@ -1260,16 +1260,20 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>〜となります</t>
+          <t>といえば</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>规定…</t>
+          <t>说起...</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>たとえば→比如</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -1277,12 +1281,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>コツ</t>
+          <t>すごく</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>诀窍，窍门</t>
+          <t>非常</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
@@ -1294,19 +1298,15 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>得をする</t>
+          <t>一度</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>获利，占便宜</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>とくをする</t>
-        </is>
-      </c>
+          <t>一次</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr"/>
     </row>
     <row r="49">
@@ -1315,12 +1315,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>...のです</t>
+          <t>どっぷり</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>因为</t>
+          <t>完全陷入</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
@@ -1332,36 +1332,36 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>といえば</t>
+          <t>...ていく</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>说起...</t>
+          <t>…持续下去</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>たとえば→比如</t>
-        </is>
-      </c>
+      <c r="E50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>きちんと</t>
+          <t>流れ</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>好好地，整洁地</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr"/>
+          <t>流程，流逝</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>ながれ</t>
+        </is>
+      </c>
       <c r="E51" t="inlineStr"/>
     </row>
     <row r="52">
@@ -1370,19 +1370,15 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>逃げ続ける</t>
+          <t>ようとする</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>持续逃跑</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>にげつづける</t>
-        </is>
-      </c>
+          <t>正想要做...，试图做...</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr"/>
     </row>
     <row r="53">
@@ -1391,15 +1387,19 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>〜ばよい</t>
+          <t>親子</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>......就好了</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr"/>
+          <t>父母与子女，亲子</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>おやこ</t>
+        </is>
+      </c>
       <c r="E53" t="inlineStr"/>
     </row>
     <row r="54">
@@ -1408,12 +1408,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ようとする</t>
+          <t>きちんと</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>正想要做...，试图做...</t>
+          <t>好好地，整洁地</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
@@ -1425,17 +1425,17 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>親子</t>
+          <t>逃げ続ける</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>父母与子女，亲子</t>
+          <t>持续逃跑</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>おやこ</t>
+          <t>にげつづける</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
@@ -1446,12 +1446,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>それくらい</t>
+          <t>〜ばよい</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>那种程度</t>
+          <t>......就好了</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
@@ -1480,16 +1480,16 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>すごく</t>
+          <t>できるだけ</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>非常</t>
+          <t>尽可能地，尽量</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
@@ -1501,20 +1501,16 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ほかの</t>
+          <t>それくらい</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>别的，其他的</t>
+          <t>那种程度</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>ほかり-&gt;其他的；除…之外，还有…</t>
-        </is>
-      </c>
+      <c r="E59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -1522,12 +1518,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>できるだけ</t>
+          <t>しっかり</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>尽可能地，尽量</t>
+          <t>好好地，牢固地</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
@@ -1539,16 +1535,20 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>しっかり</t>
+          <t>ほかの</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>好好地，牢固地</t>
+          <t>别的，其他的</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
-      <c r="E61" t="inlineStr"/>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>ほかり-&gt;其他的；除…之外，还有…</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -1556,19 +1556,15 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>教える</t>
+          <t>しゃべる</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>教，告诉</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>おしえる</t>
-        </is>
-      </c>
+          <t>说话，聊天</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr"/>
     </row>
     <row r="63">
@@ -1577,15 +1573,19 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>すでに</t>
+          <t>祝日</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>已经</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr"/>
+          <t>节日，法定假日</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>しゅくじつ</t>
+        </is>
+      </c>
       <c r="E63" t="inlineStr"/>
     </row>
     <row r="64">
@@ -1594,20 +1594,20 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>なし</t>
+          <t>教える</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>没有，无</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr"/>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>あり-&gt;有</t>
-        </is>
-      </c>
+          <t>教，告诉</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>おしえる</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>なければ</t>
+          <t>すでに</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>如果不...的话</t>
+          <t>已经</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
@@ -1632,16 +1632,20 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>ないといけない</t>
+          <t>なし</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>不得不...，必须...</t>
+          <t>没有，无</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
-      <c r="E66" t="inlineStr"/>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>あり-&gt;有</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -1649,19 +1653,15 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>少なくとも</t>
+          <t>なければ</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>至少</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>すくなくとも</t>
-        </is>
-      </c>
+          <t>如果不...的话</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr"/>
     </row>
     <row r="68">
@@ -1670,12 +1670,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>なければ</t>
+          <t>ないといけない</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>ない的假定型</t>
+          <t>不得不...，必须...</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
@@ -1687,15 +1687,19 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>しゃべる</t>
+          <t>少なくとも</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>说话，聊天</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr"/>
+          <t>至少</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>すくなくとも</t>
+        </is>
+      </c>
       <c r="E69" t="inlineStr"/>
     </row>
     <row r="70">
@@ -1704,19 +1708,15 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>祝日</t>
+          <t>なければ</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>节日，法定假日</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>しゅくじつ</t>
-        </is>
-      </c>
+          <t>ない的假定型</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr"/>
     </row>
     <row r="71">
@@ -1742,12 +1742,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>たがる</t>
+          <t>それですむ</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>（第三方）想要...</t>
+          <t>那样就行了，那样就解决了</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
@@ -1776,19 +1776,15 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>注意する</t>
+          <t>ああいう</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>注意；警告</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>ちゅういする</t>
-        </is>
-      </c>
+          <t>那样的</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr"/>
     </row>
     <row r="75">
@@ -1797,12 +1793,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>それですむ</t>
+          <t>とは</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>那样就行了，那样就解决了</t>
+          <t>所谓...；竟然...</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
@@ -1814,12 +1810,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>ああいう</t>
+          <t>ことで</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>那样的</t>
+          <t>通过...，因为...</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
@@ -1831,15 +1827,19 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>とは</t>
+          <t>いつの間に</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>所谓...；竟然...</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr"/>
+          <t>不知不觉地</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>いつのまに</t>
+        </is>
+      </c>
       <c r="E77" t="inlineStr"/>
     </row>
     <row r="78">
@@ -1848,12 +1848,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>ことで</t>
+          <t>なくす</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>通过...，因为...</t>
+          <t>弄丢，消除</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
@@ -1865,19 +1865,15 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>いつの間に</t>
+          <t>だと</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>不知不觉地</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>いつのまに</t>
-        </is>
-      </c>
+          <t>如果…的话,</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr"/>
     </row>
     <row r="80">
@@ -1886,12 +1882,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>なくす</t>
+          <t>たがる</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>弄丢，消除</t>
+          <t>（第三方）想要...</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
@@ -1903,15 +1899,19 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>だと</t>
+          <t>注意する</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>如果…的话,</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr"/>
+          <t>注意；警告</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>ちゅういする</t>
+        </is>
+      </c>
       <c r="E81" t="inlineStr"/>
     </row>
     <row r="82">

--- a/READING/3_22_07.xlsx
+++ b/READING/3_22_07.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E82"/>
+  <dimension ref="A1:F82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="2" max="2"/>
@@ -461,10 +461,15 @@
           <t>备注</t>
         </is>
       </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>History</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -482,10 +487,15 @@
           <t>ちょくせつ-&gt;直接</t>
         </is>
       </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -499,6 +509,11 @@
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -516,6 +531,11 @@
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -533,6 +553,11 @@
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -550,6 +575,11 @@
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -567,6 +597,11 @@
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -584,6 +619,11 @@
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -601,6 +641,11 @@
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -618,6 +663,11 @@
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -639,6 +689,11 @@
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -656,6 +711,11 @@
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -673,6 +733,11 @@
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -694,6 +759,11 @@
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -711,6 +781,11 @@
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -728,10 +803,15 @@
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -749,6 +829,11 @@
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -766,6 +851,11 @@
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -787,6 +877,11 @@
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -804,6 +899,11 @@
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -825,6 +925,11 @@
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -842,6 +947,11 @@
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -859,6 +969,11 @@
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -880,6 +995,11 @@
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -897,6 +1017,11 @@
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -918,6 +1043,11 @@
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -939,10 +1069,15 @@
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -956,6 +1091,11 @@
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -973,6 +1113,11 @@
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -990,6 +1135,11 @@
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1007,6 +1157,11 @@
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1028,6 +1183,11 @@
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1045,6 +1205,11 @@
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1062,6 +1227,11 @@
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1079,6 +1249,11 @@
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1096,6 +1271,11 @@
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1113,6 +1293,11 @@
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1130,6 +1315,11 @@
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1147,6 +1337,11 @@
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -1164,10 +1359,15 @@
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -1181,6 +1381,11 @@
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -1198,6 +1403,11 @@
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -1215,6 +1425,11 @@
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -1236,6 +1451,11 @@
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -1253,6 +1473,11 @@
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -1274,6 +1499,11 @@
           <t>たとえば→比如</t>
         </is>
       </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -1291,6 +1521,11 @@
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -1308,6 +1543,11 @@
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -1325,6 +1565,11 @@
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -1342,6 +1587,11 @@
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -1363,6 +1613,11 @@
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -1380,6 +1635,11 @@
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -1401,6 +1661,11 @@
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -1418,6 +1683,11 @@
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -1439,6 +1709,11 @@
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -1456,6 +1731,11 @@
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -1477,6 +1757,11 @@
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -1494,6 +1779,11 @@
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -1511,6 +1801,11 @@
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -1528,6 +1823,11 @@
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -1549,6 +1849,11 @@
           <t>ほかり-&gt;其他的；除…之外，还有…</t>
         </is>
       </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -1566,6 +1871,11 @@
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -1587,6 +1897,11 @@
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -1608,6 +1923,11 @@
         </is>
       </c>
       <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -1625,6 +1945,11 @@
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -1646,6 +1971,11 @@
           <t>あり-&gt;有</t>
         </is>
       </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -1663,6 +1993,11 @@
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -1680,6 +2015,11 @@
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr"/>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -1701,6 +2041,11 @@
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -1718,6 +2063,11 @@
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -1735,6 +2085,11 @@
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr"/>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -1752,6 +2107,11 @@
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr"/>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -1769,6 +2129,11 @@
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr"/>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -1786,6 +2151,11 @@
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr"/>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -1803,6 +2173,11 @@
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr"/>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -1820,6 +2195,11 @@
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr"/>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -1841,6 +2221,11 @@
         </is>
       </c>
       <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -1858,6 +2243,11 @@
       </c>
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr"/>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -1875,6 +2265,11 @@
       </c>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr"/>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -1892,6 +2287,11 @@
       </c>
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr"/>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -1913,6 +2313,11 @@
         </is>
       </c>
       <c r="E81" t="inlineStr"/>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -1930,6 +2335,11 @@
       </c>
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr"/>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/READING/3_22_07.xlsx
+++ b/READING/3_22_07.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\N2_2025_12\READING\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABA028D9-65A6-4D6E-8355-A08288257EAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61C4D0EC-455E-428F-9346-2ECAA8348B23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19215" yWindow="1005" windowWidth="19185" windowHeight="19995" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15405" yWindow="1005" windowWidth="22995" windowHeight="19995" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="242">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="246">
   <si>
     <t>Fre</t>
   </si>
@@ -48,9 +48,6 @@
     <t>笔直地，直接地</t>
   </si>
   <si>
-    <t>ちょくせつ-&gt;直接</t>
-  </si>
-  <si>
     <t>0</t>
   </si>
   <si>
@@ -451,9 +448,6 @@
   </si>
   <si>
     <t>别的，其他的</t>
-  </si>
-  <si>
-    <t>ほかり-&gt;其他的；除…之外，还有…</t>
   </si>
   <si>
     <t>しゃべる</t>
@@ -821,6 +815,30 @@
   </si>
   <si>
     <t>展望；预测</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ちょくせつ-&gt;直接</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ちょくせつ</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>直接</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ほかり-&gt;其他的；除…之外，还有…</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ほかり</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>其他的；除…之外，还有…</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1199,12 +1217,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F103"/>
+  <dimension ref="A1:F105"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="2" max="2" width="16" customWidth="1"/>
     <col min="3" max="3" width="23.75" customWidth="1"/>
     <col min="4" max="4" width="17" customWidth="1"/>
+    <col min="5" max="5" width="25.875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.15">
@@ -1238,38 +1257,35 @@
         <v>7</v>
       </c>
       <c r="E2" t="s">
+        <v>240</v>
+      </c>
+      <c r="F2" t="s">
         <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A3">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>10</v>
+        <v>241</v>
       </c>
       <c r="C3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" t="s">
-        <v>9</v>
+        <v>242</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A4">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F4" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.15">
@@ -1277,13 +1293,13 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.15">
@@ -1291,13 +1307,13 @@
         <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.15">
@@ -1305,13 +1321,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.15">
@@ -1319,27 +1335,27 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C8" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C9" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.15">
@@ -1347,13 +1363,13 @@
         <v>5</v>
       </c>
       <c r="B10" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C10" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.15">
@@ -1361,16 +1377,13 @@
         <v>5</v>
       </c>
       <c r="B11" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C11" t="s">
-        <v>28</v>
-      </c>
-      <c r="D11" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.15">
@@ -1378,13 +1391,16 @@
         <v>5</v>
       </c>
       <c r="B12" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C12" t="s">
-        <v>31</v>
+        <v>27</v>
+      </c>
+      <c r="D12" t="s">
+        <v>28</v>
       </c>
       <c r="F12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.15">
@@ -1392,30 +1408,27 @@
         <v>5</v>
       </c>
       <c r="B13" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C13" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F13" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B14" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C14" t="s">
-        <v>35</v>
-      </c>
-      <c r="D14" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="F14" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.15">
@@ -1423,58 +1436,61 @@
         <v>4</v>
       </c>
       <c r="B15" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="C15" t="s">
-        <v>38</v>
+        <v>34</v>
+      </c>
+      <c r="D15" t="s">
+        <v>35</v>
       </c>
       <c r="F15" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A16">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B16" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C16" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="F16" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A17">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B17" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C17" t="s">
-        <v>42</v>
-      </c>
-      <c r="D17" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="F17" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A18">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B18" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C18" t="s">
-        <v>45</v>
+        <v>41</v>
+      </c>
+      <c r="D18" t="s">
+        <v>42</v>
       </c>
       <c r="F18" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.15">
@@ -1482,16 +1498,13 @@
         <v>3</v>
       </c>
       <c r="B19" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C19" t="s">
-        <v>47</v>
-      </c>
-      <c r="D19" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F19" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.15">
@@ -1499,13 +1512,16 @@
         <v>3</v>
       </c>
       <c r="B20" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C20" t="s">
-        <v>50</v>
+        <v>46</v>
+      </c>
+      <c r="D20" t="s">
+        <v>47</v>
       </c>
       <c r="F20" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.15">
@@ -1513,16 +1529,13 @@
         <v>3</v>
       </c>
       <c r="B21" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C21" t="s">
-        <v>52</v>
-      </c>
-      <c r="D21" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F21" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.15">
@@ -1530,13 +1543,16 @@
         <v>3</v>
       </c>
       <c r="B22" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C22" t="s">
-        <v>55</v>
+        <v>51</v>
+      </c>
+      <c r="D22" t="s">
+        <v>52</v>
       </c>
       <c r="F22" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.15">
@@ -1544,13 +1560,13 @@
         <v>3</v>
       </c>
       <c r="B23" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C23" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="F23" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.15">
@@ -1558,16 +1574,13 @@
         <v>3</v>
       </c>
       <c r="B24" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C24" t="s">
-        <v>59</v>
-      </c>
-      <c r="D24" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="F24" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.15">
@@ -1575,13 +1588,16 @@
         <v>3</v>
       </c>
       <c r="B25" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C25" t="s">
-        <v>62</v>
+        <v>58</v>
+      </c>
+      <c r="D25" t="s">
+        <v>59</v>
       </c>
       <c r="F25" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.15">
@@ -1589,16 +1605,13 @@
         <v>3</v>
       </c>
       <c r="B26" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C26" t="s">
-        <v>64</v>
-      </c>
-      <c r="D26" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="F26" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.15">
@@ -1606,16 +1619,16 @@
         <v>3</v>
       </c>
       <c r="B27" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C27" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D27" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="F27" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.15">
@@ -1623,27 +1636,30 @@
         <v>3</v>
       </c>
       <c r="B28" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C28" t="s">
-        <v>70</v>
+        <v>66</v>
+      </c>
+      <c r="D28" t="s">
+        <v>67</v>
       </c>
       <c r="F28" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A29">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B29" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C29" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F29" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.15">
@@ -1651,13 +1667,13 @@
         <v>2</v>
       </c>
       <c r="B30" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C30" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="F30" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.15">
@@ -1665,13 +1681,13 @@
         <v>2</v>
       </c>
       <c r="B31" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C31" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="F31" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.15">
@@ -1679,16 +1695,13 @@
         <v>2</v>
       </c>
       <c r="B32" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C32" t="s">
-        <v>78</v>
-      </c>
-      <c r="D32" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F32" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.15">
@@ -1696,13 +1709,16 @@
         <v>2</v>
       </c>
       <c r="B33" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C33" t="s">
-        <v>81</v>
+        <v>77</v>
+      </c>
+      <c r="D33" t="s">
+        <v>78</v>
       </c>
       <c r="F33" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.15">
@@ -1710,13 +1726,13 @@
         <v>2</v>
       </c>
       <c r="B34" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C34" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="F34" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.15">
@@ -1724,13 +1740,13 @@
         <v>2</v>
       </c>
       <c r="B35" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C35" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="F35" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.15">
@@ -1738,13 +1754,13 @@
         <v>2</v>
       </c>
       <c r="B36" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C36" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="F36" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.15">
@@ -1752,13 +1768,13 @@
         <v>2</v>
       </c>
       <c r="B37" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C37" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="F37" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.15">
@@ -1766,13 +1782,13 @@
         <v>2</v>
       </c>
       <c r="B38" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C38" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="F38" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.15">
@@ -1780,13 +1796,13 @@
         <v>2</v>
       </c>
       <c r="B39" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C39" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="F39" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.15">
@@ -1794,41 +1810,41 @@
         <v>2</v>
       </c>
       <c r="B40" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C40" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="F40" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A41">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B41" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C41" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="F41" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A42">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B42" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C42" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F42" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.15">
@@ -1836,13 +1852,13 @@
         <v>2</v>
       </c>
       <c r="B43" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C43" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="F43" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.15">
@@ -1850,16 +1866,13 @@
         <v>2</v>
       </c>
       <c r="B44" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C44" t="s">
-        <v>103</v>
-      </c>
-      <c r="D44" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="F44" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.15">
@@ -1867,13 +1880,16 @@
         <v>2</v>
       </c>
       <c r="B45" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C45" t="s">
-        <v>106</v>
+        <v>102</v>
+      </c>
+      <c r="D45" t="s">
+        <v>103</v>
       </c>
       <c r="F45" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.15">
@@ -1881,16 +1897,13 @@
         <v>2</v>
       </c>
       <c r="B46" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C46" t="s">
-        <v>108</v>
-      </c>
-      <c r="E46" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="F46" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.15">
@@ -1898,13 +1911,16 @@
         <v>2</v>
       </c>
       <c r="B47" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C47" t="s">
-        <v>111</v>
+        <v>107</v>
+      </c>
+      <c r="E47" t="s">
+        <v>108</v>
       </c>
       <c r="F47" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.15">
@@ -1912,13 +1928,13 @@
         <v>2</v>
       </c>
       <c r="B48" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C48" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="F48" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.15">
@@ -1926,13 +1942,13 @@
         <v>2</v>
       </c>
       <c r="B49" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="C49" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="F49" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.15">
@@ -1940,13 +1956,13 @@
         <v>2</v>
       </c>
       <c r="B50" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C50" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="F50" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.15">
@@ -1954,30 +1970,30 @@
         <v>2</v>
       </c>
       <c r="B51" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="C51" t="s">
-        <v>119</v>
-      </c>
-      <c r="D51" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F51" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A52">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B52" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="C52" t="s">
-        <v>122</v>
+        <v>118</v>
+      </c>
+      <c r="D52" t="s">
+        <v>119</v>
       </c>
       <c r="F52" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.15">
@@ -1985,16 +2001,13 @@
         <v>1</v>
       </c>
       <c r="B53" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="C53" t="s">
-        <v>124</v>
-      </c>
-      <c r="D53" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F53" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.15">
@@ -2002,13 +2015,16 @@
         <v>1</v>
       </c>
       <c r="B54" t="s">
-        <v>225</v>
+        <v>122</v>
       </c>
       <c r="C54" t="s">
-        <v>126</v>
+        <v>123</v>
+      </c>
+      <c r="D54" t="s">
+        <v>124</v>
       </c>
       <c r="F54" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.15">
@@ -2016,16 +2032,13 @@
         <v>1</v>
       </c>
       <c r="B55" t="s">
-        <v>127</v>
+        <v>223</v>
       </c>
       <c r="C55" t="s">
-        <v>128</v>
-      </c>
-      <c r="D55" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="F55" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.15">
@@ -2033,13 +2046,16 @@
         <v>1</v>
       </c>
       <c r="B56" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="C56" t="s">
-        <v>131</v>
+        <v>127</v>
+      </c>
+      <c r="D56" t="s">
+        <v>128</v>
       </c>
       <c r="F56" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.15">
@@ -2047,16 +2063,13 @@
         <v>1</v>
       </c>
       <c r="B57" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C57" t="s">
-        <v>133</v>
-      </c>
-      <c r="D57" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="F57" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.15">
@@ -2064,13 +2077,16 @@
         <v>1</v>
       </c>
       <c r="B58" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="C58" t="s">
-        <v>136</v>
+        <v>132</v>
+      </c>
+      <c r="D58" t="s">
+        <v>133</v>
       </c>
       <c r="F58" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.15">
@@ -2078,13 +2094,13 @@
         <v>1</v>
       </c>
       <c r="B59" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C59" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="F59" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.15">
@@ -2092,13 +2108,13 @@
         <v>1</v>
       </c>
       <c r="B60" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="C60" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="F60" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.15">
@@ -2106,47 +2122,41 @@
         <v>1</v>
       </c>
       <c r="B61" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C61" t="s">
-        <v>142</v>
-      </c>
-      <c r="E61" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="F61" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A62">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B62" t="s">
-        <v>144</v>
+        <v>244</v>
       </c>
       <c r="C62" t="s">
-        <v>145</v>
-      </c>
-      <c r="F62" t="s">
-        <v>14</v>
+        <v>245</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A63">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B63" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="C63" t="s">
-        <v>147</v>
-      </c>
-      <c r="D63" t="s">
-        <v>148</v>
+        <v>141</v>
+      </c>
+      <c r="E63" t="s">
+        <v>243</v>
       </c>
       <c r="F63" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.15">
@@ -2154,16 +2164,13 @@
         <v>0</v>
       </c>
       <c r="B64" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="C64" t="s">
-        <v>150</v>
-      </c>
-      <c r="D64" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="F64" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.15">
@@ -2171,13 +2178,16 @@
         <v>0</v>
       </c>
       <c r="B65" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="C65" t="s">
-        <v>153</v>
+        <v>145</v>
+      </c>
+      <c r="D65" t="s">
+        <v>146</v>
       </c>
       <c r="F65" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.15">
@@ -2185,16 +2195,16 @@
         <v>0</v>
       </c>
       <c r="B66" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="C66" t="s">
-        <v>155</v>
-      </c>
-      <c r="E66" t="s">
-        <v>156</v>
+        <v>148</v>
+      </c>
+      <c r="D66" t="s">
+        <v>149</v>
       </c>
       <c r="F66" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.15">
@@ -2202,13 +2212,13 @@
         <v>0</v>
       </c>
       <c r="B67" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="C67" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="F67" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.15">
@@ -2216,13 +2226,16 @@
         <v>0</v>
       </c>
       <c r="B68" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="C68" t="s">
-        <v>160</v>
+        <v>153</v>
+      </c>
+      <c r="E68" t="s">
+        <v>154</v>
       </c>
       <c r="F68" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.15">
@@ -2230,16 +2243,13 @@
         <v>0</v>
       </c>
       <c r="B69" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="C69" t="s">
-        <v>162</v>
-      </c>
-      <c r="D69" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="F69" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.15">
@@ -2250,10 +2260,10 @@
         <v>157</v>
       </c>
       <c r="C70" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="F70" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.15">
@@ -2261,13 +2271,16 @@
         <v>0</v>
       </c>
       <c r="B71" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="C71" t="s">
-        <v>166</v>
+        <v>160</v>
+      </c>
+      <c r="D71" t="s">
+        <v>161</v>
       </c>
       <c r="F71" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.15">
@@ -2275,13 +2288,13 @@
         <v>0</v>
       </c>
       <c r="B72" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="C72" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="F72" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.15">
@@ -2289,13 +2302,13 @@
         <v>0</v>
       </c>
       <c r="B73" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="C73" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="F73" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.15">
@@ -2303,13 +2316,13 @@
         <v>0</v>
       </c>
       <c r="B74" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="C74" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="F74" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.15">
@@ -2317,13 +2330,13 @@
         <v>0</v>
       </c>
       <c r="B75" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="C75" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="F75" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.15">
@@ -2331,13 +2344,13 @@
         <v>0</v>
       </c>
       <c r="B76" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="C76" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="F76" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.15">
@@ -2345,16 +2358,13 @@
         <v>0</v>
       </c>
       <c r="B77" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="C77" t="s">
-        <v>178</v>
-      </c>
-      <c r="D77" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="F77" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.15">
@@ -2362,13 +2372,13 @@
         <v>0</v>
       </c>
       <c r="B78" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="C78" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="F78" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.15">
@@ -2376,13 +2386,16 @@
         <v>0</v>
       </c>
       <c r="B79" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="C79" t="s">
-        <v>183</v>
+        <v>176</v>
+      </c>
+      <c r="D79" t="s">
+        <v>177</v>
       </c>
       <c r="F79" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.15">
@@ -2390,13 +2403,13 @@
         <v>0</v>
       </c>
       <c r="B80" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="C80" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="F80" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.15">
@@ -2404,16 +2417,13 @@
         <v>0</v>
       </c>
       <c r="B81" t="s">
-        <v>224</v>
+        <v>180</v>
       </c>
       <c r="C81" t="s">
-        <v>186</v>
-      </c>
-      <c r="D81" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="F81" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.15">
@@ -2421,35 +2431,44 @@
         <v>0</v>
       </c>
       <c r="B82" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="C82" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="F82" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A83">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B83" t="s">
-        <v>190</v>
+        <v>222</v>
       </c>
       <c r="C83" t="s">
-        <v>191</v>
+        <v>184</v>
+      </c>
+      <c r="D83" t="s">
+        <v>185</v>
+      </c>
+      <c r="F83" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A84">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B84" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="C84" t="s">
-        <v>193</v>
+        <v>187</v>
+      </c>
+      <c r="F84" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.15">
@@ -2457,13 +2476,10 @@
         <v>2</v>
       </c>
       <c r="B85" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="C85" t="s">
-        <v>195</v>
-      </c>
-      <c r="D85" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.15">
@@ -2471,10 +2487,10 @@
         <v>2</v>
       </c>
       <c r="B86" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="C86" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.15">
@@ -2482,10 +2498,13 @@
         <v>2</v>
       </c>
       <c r="B87" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="C87" t="s">
-        <v>200</v>
+        <v>193</v>
+      </c>
+      <c r="D87" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.15">
@@ -2493,10 +2512,10 @@
         <v>2</v>
       </c>
       <c r="B88" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="C88" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.15">
@@ -2504,13 +2523,10 @@
         <v>2</v>
       </c>
       <c r="B89" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="C89" t="s">
-        <v>205</v>
-      </c>
-      <c r="D89" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.15">
@@ -2518,10 +2534,10 @@
         <v>2</v>
       </c>
       <c r="B90" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="C90" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.15">
@@ -2529,13 +2545,13 @@
         <v>2</v>
       </c>
       <c r="B91" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="C91" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="D91" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.15">
@@ -2543,13 +2559,10 @@
         <v>2</v>
       </c>
       <c r="B92" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="C92" t="s">
-        <v>212</v>
-      </c>
-      <c r="D92" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.15">
@@ -2557,13 +2570,13 @@
         <v>2</v>
       </c>
       <c r="B93" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="C93" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="D93" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.15">
@@ -2571,13 +2584,13 @@
         <v>2</v>
       </c>
       <c r="B94" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="C94" t="s">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="D94" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.15">
@@ -2585,10 +2598,13 @@
         <v>2</v>
       </c>
       <c r="B95" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="C95" t="s">
-        <v>221</v>
+        <v>213</v>
+      </c>
+      <c r="D95" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.15">
@@ -2596,10 +2612,13 @@
         <v>2</v>
       </c>
       <c r="B96" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="C96" t="s">
-        <v>223</v>
+        <v>217</v>
+      </c>
+      <c r="D96" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.15">
@@ -2607,10 +2626,10 @@
         <v>2</v>
       </c>
       <c r="B97" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="C97" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.15">
@@ -2618,10 +2637,10 @@
         <v>2</v>
       </c>
       <c r="B98" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="C98" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.15">
@@ -2629,13 +2648,10 @@
         <v>2</v>
       </c>
       <c r="B99" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="C99" t="s">
-        <v>231</v>
-      </c>
-      <c r="D99" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.15">
@@ -2643,21 +2659,24 @@
         <v>2</v>
       </c>
       <c r="B100" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="C100" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="101" spans="1:4" ht="18.75" x14ac:dyDescent="0.4">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A101">
         <v>2</v>
       </c>
       <c r="B101" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="C101" t="s">
-        <v>236</v>
+        <v>229</v>
+      </c>
+      <c r="D101" t="s">
+        <v>230</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.15">
@@ -2665,24 +2684,46 @@
         <v>2</v>
       </c>
       <c r="B102" t="s">
+        <v>231</v>
+      </c>
+      <c r="C102" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A103">
+        <v>2</v>
+      </c>
+      <c r="B103" t="s">
+        <v>233</v>
+      </c>
+      <c r="C103" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A104">
+        <v>2</v>
+      </c>
+      <c r="B104" t="s">
+        <v>235</v>
+      </c>
+      <c r="C104" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A105">
+        <v>2</v>
+      </c>
+      <c r="B105" t="s">
         <v>237</v>
       </c>
-      <c r="C102" t="s">
+      <c r="C105" t="s">
+        <v>239</v>
+      </c>
+      <c r="D105" t="s">
         <v>238</v>
-      </c>
-    </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A103">
-        <v>2</v>
-      </c>
-      <c r="B103" t="s">
-        <v>239</v>
-      </c>
-      <c r="C103" t="s">
-        <v>241</v>
-      </c>
-      <c r="D103" t="s">
-        <v>240</v>
       </c>
     </row>
   </sheetData>
